--- a/generated/spreadsheet/outline-planning-outline.xlsx
+++ b/generated/spreadsheet/outline-planning-outline.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I180"/>
+  <dimension ref="A1:I179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -568,14 +568,14 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Application sub type</t>
+          <t>Planning authority</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Further classification of the application type for specific variations within the main application type</t>
+          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -599,19 +599,19 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Planning authority</t>
+          <t>Submission date</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
+          <t>Date the application is submitted in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -630,19 +630,19 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Submission date</t>
+          <t>Modules[]</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Date the application is submitted in YYYY-MM-DD format</t>
+          <t>List of required modules for this application that can be used to validate the application</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -661,14 +661,18 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Modules[]</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr"/>
+          <t>Documents[]</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>List of required modules for this application that can be used to validate the application</t>
+          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -697,13 +701,13 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
+          <t>The name or title of the document</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -732,13 +736,13 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>The name or title of the document</t>
+          <t>Brief description of what the document contains</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -748,7 +752,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -767,23 +771,23 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Document types[]</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Brief description of what the document contains</t>
+          <t>List of codelist references that the document covers</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -802,18 +806,18 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Document types[]</t>
+          <t>Uploaded date</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>List of codelist references that the document covers</t>
+          <t>The date the document was uploaded to the application</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -837,23 +841,27 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Uploaded date</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr"/>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Base64</t>
+        </is>
+      </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>The date the document was uploaded to the application</t>
+          <t>Base64-encoded content of the file for inline file uploads</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -877,12 +885,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Base64</t>
+          <t>Filename</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Base64-encoded content of the file for inline file uploads</t>
+          <t>Name of the file being uploaded</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -892,7 +900,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -916,12 +924,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Filename</t>
+          <t>MIME type</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Name of the file being uploaded</t>
+          <t>The file's MIME type such as application/pdf or image/jpeg</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -931,7 +939,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -955,17 +963,17 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>MIME type</t>
+          <t>File size</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>The file's MIME type such as application/pdf or image/jpeg</t>
+          <t>Size of the file in bytes that can be used to enforce limits</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -984,22 +992,18 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Documents[]</t>
+          <t>Fee</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>File size</t>
-        </is>
-      </c>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Size of the file in bytes that can be used to enforce limits</t>
+          <t>The total amount due for the application fee</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1009,7 +1013,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1028,13 +1032,13 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Amount</t>
+          <t>Amount paid</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>The total amount due for the application fee</t>
+          <t>The amount paid towards the application fee</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1063,48 +1067,48 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Amount paid</t>
+          <t>Transactions[]</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>The amount paid towards the application fee</t>
+          <t>References to payments or financial transactions related to this application</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n"/>
-      <c r="B19" s="2" t="n"/>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Agent contact details</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information if an agent is being used.</t>
+        </is>
+      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Fee</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Transactions[]</t>
-        </is>
-      </c>
+          <t>Agent reference</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr"/>
+      <c r="E19" s="2" t="inlineStr"/>
       <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>References to payments or financial transactions related to this application</t>
+          <t>A reference to an agent object</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1114,32 +1118,28 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Agent contact details</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Name and contact information if an agent is being used.</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="n"/>
+      <c r="B20" s="2" t="n"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Agent reference</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr"/>
+          <t>Contact details</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
       <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>A reference to an agent object</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1163,14 +1163,18 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Phone number</t>
+        </is>
+      </c>
       <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1180,7 +1184,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1199,18 +1203,18 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Contact priority</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1220,51 +1224,47 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n"/>
-      <c r="B23" s="2" t="n"/>
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Agent details</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information if an agent is being used.</t>
+        </is>
+      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
+          <t>agent</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Contact priority</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr"/>
       <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>Agent details</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>Name and contact information if an agent is being used.</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="n"/>
+      <c r="B24" s="2" t="n"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>agent</t>
@@ -1272,14 +1272,18 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
       <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1289,7 +1293,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1308,13 +1312,13 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1324,7 +1328,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1343,13 +1347,13 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr"/>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1378,13 +1382,13 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr"/>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1413,13 +1417,13 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1429,7 +1433,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1443,18 +1447,14 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr"/>
       <c r="F29" s="2" t="inlineStr"/>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>The name of a company (that the agent works for)</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1478,19 +1478,19 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>User role</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="2" t="inlineStr"/>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>The name of a company (that the agent works for)</t>
+          <t>The role of the named individual. Agent or proxy</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -1500,58 +1500,58 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n"/>
-      <c r="B31" s="2" t="n"/>
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Applicant contact details</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Telephone number and email address of the applicant.</t>
+        </is>
+      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>agent</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>User role</t>
-        </is>
-      </c>
+          <t>Applicant reference</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr"/>
       <c r="E31" s="2" t="inlineStr"/>
       <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>The role of the named individual. Agent or proxy</t>
+          <t>Reference to match contact details to a named individual from the applicant details component</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>Applicant contact details</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>Telephone number and email address of the applicant.</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="n"/>
+      <c r="B32" s="2" t="n"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Applicant reference</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr"/>
+          <t>Contact details</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
       <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Reference to match contact details to a named individual from the applicant details component</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -1575,14 +1575,18 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Phone number</t>
+        </is>
+      </c>
       <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -1592,7 +1596,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1611,18 +1615,18 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Contact priority</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -1632,51 +1636,47 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n"/>
-      <c r="B35" s="2" t="n"/>
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Applicant details</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information for the parties making the application.</t>
+        </is>
+      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
+          <t>Applicants[]</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>Contact priority</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr"/>
       <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>Applicant details</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>Name and contact information for the parties making the application.</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="n"/>
+      <c r="B36" s="2" t="n"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>Applicants[]</t>
@@ -1684,14 +1684,18 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
       <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -1701,7 +1705,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1720,13 +1724,13 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -1736,7 +1740,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1755,13 +1759,13 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr"/>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -1790,13 +1794,13 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr"/>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -1825,13 +1829,13 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -1841,72 +1845,68 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n"/>
-      <c r="B41" s="2" t="n"/>
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Biodiversity net gain</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>How any natural habitats on the development site will be improved by the proposed works.</t>
+        </is>
+      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Applicants[]</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Biodiversity gain condition applies</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr"/>
+      <c r="E41" s="2" t="inlineStr"/>
       <c r="F41" s="2" t="inlineStr"/>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Does the applicant believe the Biodiversity Gain Condition applies to this application</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>Biodiversity net gain</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>How any natural habitats on the development site will be improved by the proposed works.</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="n"/>
+      <c r="B42" s="2" t="n"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity gain condition applies</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr"/>
+          <t>Biodiversity gain condition exemption reason[]</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Exemption type</t>
+        </is>
+      </c>
       <c r="E42" s="2" t="inlineStr"/>
       <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Does the applicant believe the Biodiversity Gain Condition applies to this application</t>
+          <t>The type of biodiversity gain exemption from the bng-exemption-type enum</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -1925,19 +1925,19 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Exemption type</t>
+          <t>Reason</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr"/>
       <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>The type of biodiversity gain exemption from the bng-exemption-type enum</t>
+          <t>The reason the exemption applies to this proposal</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -1951,24 +1951,24 @@
       <c r="B44" s="2" t="n"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity gain condition exemption reason[]</t>
+          <t>Biodiversity net gain details</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Reason</t>
+          <t>Pre development date</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr"/>
       <c r="F44" s="2" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>The reason the exemption applies to this proposal</t>
+          <t>Date of pre-development biodiversity value calculation, must align with application or justified earlier date</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -1987,19 +1987,19 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Pre development date</t>
+          <t>Pre development biodiversity value</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
       <c r="F45" s="2" t="inlineStr"/>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Date of pre-development biodiversity value calculation, must align with application or justified earlier date</t>
+          <t>Calculated biodiversity value in Habitat Biodiversity Units</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
@@ -2018,24 +2018,24 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Pre development biodiversity value</t>
+          <t>Earlier date reason</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr"/>
       <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Calculated biodiversity value in Habitat Biodiversity Units</t>
+          <t>Reason for using a pre-development date that is earlier than the application submission</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2049,19 +2049,19 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Earlier date reason</t>
+          <t>Habitat loss after 2020</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr"/>
       <c r="F47" s="2" t="inlineStr"/>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Reason for using a pre-development date that is earlier than the application submission</t>
+          <t>Indicates whether there has been degradation of onsite habitat(s) after 30 Jan 2020</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -2080,24 +2080,28 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Habitat loss after 2020</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr"/>
+          <t>Habitat loss details</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Loss date</t>
+        </is>
+      </c>
       <c r="F48" s="2" t="inlineStr"/>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether there has been degradation of onsite habitat(s) after 30 Jan 2020</t>
+          <t>Date the activity causing habitat loss or degradation occurred</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2116,18 +2120,18 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Loss date</t>
+          <t>Pre loss biodiversity value</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr"/>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Date the activity causing habitat loss or degradation occurred</t>
+          <t>Biodiversity value immediately before habitat loss or degradation occurred, measured in Habitat Biodiversity Units</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
@@ -2151,23 +2155,23 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Pre loss biodiversity value</t>
+          <t>Supporting evidence</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr"/>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity value immediately before habitat loss or degradation occurred, measured in Habitat Biodiversity Units</t>
+          <t>Description or reference to supporting documents for habitat loss or degradation evidence</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2181,28 +2185,24 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Habitat loss details</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>Supporting evidence</t>
-        </is>
-      </c>
+          <t>Metric publication date</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr"/>
       <c r="F51" s="2" t="inlineStr"/>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Description or reference to supporting documents for habitat loss or degradation evidence</t>
+          <t>Publication date of the biodiversity metric tool used for calculations</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2216,19 +2216,19 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Metric publication date</t>
+          <t>Irreplaceable habitats</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr"/>
       <c r="F52" s="2" t="inlineStr"/>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Publication date of the biodiversity metric tool used for calculations</t>
+          <t>Indicates whether the site contains any irreplaceable habitats</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
@@ -2247,24 +2247,24 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Irreplaceable habitats</t>
+          <t>Irreplaceable habitats details</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr"/>
       <c r="F53" s="2" t="inlineStr"/>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether the site contains any irreplaceable habitats</t>
+          <t>Description and references for any irreplaceable habitats identified on the site</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2278,14 +2278,18 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Irreplaceable habitats details</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr"/>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="F54" s="2" t="inlineStr"/>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Description and references for any irreplaceable habitats identified on the site</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -2295,32 +2299,32 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n"/>
-      <c r="B55" s="2" t="n"/>
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Checklist</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
+        </is>
+      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity net gain details</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>National requirement types[]</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr"/>
+      <c r="E55" s="2" t="inlineStr"/>
       <c r="F55" s="2" t="inlineStr"/>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>List of the document types required for the given application type</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -2337,17 +2341,17 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Checklist</t>
+          <t>Conflict of interest</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
+          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>National requirement types[]</t>
+          <t>Conflict to declare</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr"/>
@@ -2355,12 +2359,12 @@
       <c r="F56" s="2" t="inlineStr"/>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>List of the document types required for the given application type</t>
+          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -2370,19 +2374,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>Conflict of interest</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
-        </is>
-      </c>
+      <c r="A57" s="2" t="n"/>
+      <c r="B57" s="2" t="n"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Conflict to declare</t>
+          <t>Conflict person name</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr"/>
@@ -2390,17 +2386,17 @@
       <c r="F57" s="2" t="inlineStr"/>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
+          <t>Name of the individual with the conflict of interest that matches one of the names provided in applicants/agent section</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2409,7 +2405,7 @@
       <c r="B58" s="2" t="n"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Conflict person name</t>
+          <t>Conflict details</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr"/>
@@ -2417,7 +2413,7 @@
       <c r="F58" s="2" t="inlineStr"/>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Name of the individual with the conflict of interest that matches one of the names provided in applicants/agent section</t>
+          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -2432,11 +2428,19 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n"/>
-      <c r="B59" s="2" t="n"/>
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Declaration</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Signed and dated verification of the application's accuracy.</t>
+        </is>
+      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Conflict details</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr"/>
@@ -2444,7 +2448,7 @@
       <c r="F59" s="2" t="inlineStr"/>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
+          <t>A name of a person</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -2454,24 +2458,16 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>Declaration</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>Signed and dated verification of the application's accuracy.</t>
-        </is>
-      </c>
+      <c r="A60" s="2" t="n"/>
+      <c r="B60" s="2" t="n"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr"/>
@@ -2479,12 +2475,12 @@
       <c r="F60" s="2" t="inlineStr"/>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>A name of a person</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
@@ -2498,7 +2494,7 @@
       <c r="B61" s="2" t="n"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr"/>
@@ -2506,12 +2502,12 @@
       <c r="F61" s="2" t="inlineStr"/>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
@@ -2521,24 +2517,36 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n"/>
-      <c r="B62" s="2" t="n"/>
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Employment</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>How the proposed development will impact existing and proposed employee numbers</t>
+        </is>
+      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr"/>
+          <t>Existing employees</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
       <c r="E62" s="2" t="inlineStr"/>
       <c r="F62" s="2" t="inlineStr"/>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Number of full-time employees</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
@@ -2548,16 +2556,8 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>Employment</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>How the proposed development will impact existing and proposed employee numbers</t>
-        </is>
-      </c>
+      <c r="A63" s="2" t="n"/>
+      <c r="B63" s="2" t="n"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>Existing employees</t>
@@ -2565,14 +2565,14 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Part-time</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr"/>
       <c r="F63" s="2" t="inlineStr"/>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Number of full-time employees</t>
+          <t>Number of part-time employees</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -2596,14 +2596,14 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Part-time</t>
+          <t>Total FTE</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr"/>
       <c r="F64" s="2" t="inlineStr"/>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Number of part-time employees</t>
+          <t>Total full-time equivalent (FTE)</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -2622,19 +2622,19 @@
       <c r="B65" s="2" t="n"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Existing employees</t>
+          <t>Proposed employees</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Total FTE</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr"/>
       <c r="F65" s="2" t="inlineStr"/>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Total full-time equivalent (FTE)</t>
+          <t>Number of full-time employees</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -2658,14 +2658,14 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Part-time</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr"/>
       <c r="F66" s="2" t="inlineStr"/>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Number of full-time employees</t>
+          <t>Number of part-time employees</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -2689,14 +2689,14 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Part-time</t>
+          <t>Total FTE</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr"/>
       <c r="F67" s="2" t="inlineStr"/>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Number of part-time employees</t>
+          <t>Total full-time equivalent (FTE)</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -2711,28 +2711,36 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n"/>
-      <c r="B68" s="2" t="n"/>
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Existing use</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>How the site is currently being used.</t>
+        </is>
+      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Proposed employees</t>
+          <t>Existing use details[]</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Total FTE</t>
+          <t>Use</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr"/>
       <c r="F68" s="2" t="inlineStr"/>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Total full-time equivalent (FTE)</t>
+          <t>A use class or type of use</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
@@ -2742,16 +2750,8 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>Existing use</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>How the site is currently being used.</t>
-        </is>
-      </c>
+      <c r="A69" s="2" t="n"/>
+      <c r="B69" s="2" t="n"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>Existing use details[]</t>
@@ -2759,24 +2759,24 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Use</t>
+          <t>Use details</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr"/>
       <c r="F69" s="2" t="inlineStr"/>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>A use class or type of use</t>
+          <t>Further detail of the use</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2790,14 +2790,14 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Use details</t>
+          <t>Land part</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr"/>
       <c r="F70" s="2" t="inlineStr"/>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Further detail of the use</t>
+          <t>Which part of the land the use relates to</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2816,24 +2816,20 @@
       <c r="B71" s="2" t="n"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Existing use details[]</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>Land part</t>
-        </is>
-      </c>
+          <t>Site vacant</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr"/>
       <c r="E71" s="2" t="inlineStr"/>
       <c r="F71" s="2" t="inlineStr"/>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Which part of the land the use relates to</t>
+          <t>Is the site currently vacant</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
@@ -2847,7 +2843,7 @@
       <c r="B72" s="2" t="n"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Site vacant</t>
+          <t>Last use details</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr"/>
@@ -2855,17 +2851,17 @@
       <c r="F72" s="2" t="inlineStr"/>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Is the site currently vacant</t>
+          <t>Description of the last use of the site</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2874,7 +2870,7 @@
       <c r="B73" s="2" t="n"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Last use details</t>
+          <t>Last use end date</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr"/>
@@ -2882,12 +2878,12 @@
       <c r="F73" s="2" t="inlineStr"/>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Description of the last use of the site</t>
+          <t>Date the last use ended (YYYY-MM-DD format)</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
@@ -2901,7 +2897,7 @@
       <c r="B74" s="2" t="n"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Last use end date</t>
+          <t>Is contaminated land</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr"/>
@@ -2909,17 +2905,17 @@
       <c r="F74" s="2" t="inlineStr"/>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Date the last use ended (YYYY-MM-DD format)</t>
+          <t>Is the site known to be contaminated?</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2924,7 @@
       <c r="B75" s="2" t="n"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Is contaminated land</t>
+          <t>Is suspected contaminated land</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr"/>
@@ -2936,7 +2932,7 @@
       <c r="F75" s="2" t="inlineStr"/>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Is the site known to be contaminated?</t>
+          <t>Is the site suspected of contamination?</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -2955,7 +2951,7 @@
       <c r="B76" s="2" t="n"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Is suspected contaminated land</t>
+          <t>Proposed use contamination risk</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr"/>
@@ -2963,7 +2959,7 @@
       <c r="F76" s="2" t="inlineStr"/>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Is the site suspected of contamination?</t>
+          <t>Is the proposed use vulnerable to the presence of contamination?</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -2982,7 +2978,7 @@
       <c r="B77" s="2" t="n"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Proposed use contamination risk</t>
+          <t>Contamination assessment</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr"/>
@@ -2990,26 +2986,34 @@
       <c r="F77" s="2" t="inlineStr"/>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>Is the proposed use vulnerable to the presence of contamination?</t>
+          <t>Reference to contamination assessment document</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n"/>
-      <c r="B78" s="2" t="n"/>
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Flood risk assessment</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Results of any flood risk assessments made for the development site</t>
+        </is>
+      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Contamination assessment</t>
+          <t>Flood risk area</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr"/>
@@ -3017,34 +3021,26 @@
       <c r="F78" s="2" t="inlineStr"/>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Reference to contamination assessment document</t>
+          <t>Is the site within an area at risk of flooding?</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>Flood risk assessment</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>Results of any flood risk assessments made for the development site</t>
-        </is>
-      </c>
+      <c r="A79" s="2" t="n"/>
+      <c r="B79" s="2" t="n"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Flood risk area</t>
+          <t>Data provided by</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr"/>
@@ -3052,17 +3048,17 @@
       <c r="F79" s="2" t="inlineStr"/>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Is the site within an area at risk of flooding?</t>
+          <t>Who provided the data: Applicant or System/Service?</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3071,7 +3067,7 @@
       <c r="B80" s="2" t="n"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Data provided by</t>
+          <t>Flood risk assessment</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr"/>
@@ -3079,12 +3075,12 @@
       <c r="F80" s="2" t="inlineStr"/>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Who provided the data: Applicant or System/Service?</t>
+          <t>Reference of the flood risk assessment document</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
@@ -3098,7 +3094,7 @@
       <c r="B81" s="2" t="n"/>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Flood risk assessment</t>
+          <t>Within 20m watercourse</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr"/>
@@ -3106,17 +3102,17 @@
       <c r="F81" s="2" t="inlineStr"/>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Reference of the flood risk assessment document</t>
+          <t>Whether the development is within 20 metres of a watercourse</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3121,7 @@
       <c r="B82" s="2" t="n"/>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Within 20m watercourse</t>
+          <t>Increases flood risk</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr"/>
@@ -3133,7 +3129,7 @@
       <c r="F82" s="2" t="inlineStr"/>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Whether the development is within 20 metres of a watercourse</t>
+          <t>Whether the development increases flood risk</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -3152,7 +3148,7 @@
       <c r="B83" s="2" t="n"/>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Increases flood risk</t>
+          <t>Surface water disposal[]</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr"/>
@@ -3160,12 +3156,12 @@
       <c r="F83" s="2" t="inlineStr"/>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Whether the development increases flood risk</t>
+          <t>Method for disposing of surface water</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
@@ -3175,19 +3171,31 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n"/>
-      <c r="B84" s="2" t="n"/>
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Hours of operation</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Proposed operating hours if the proposed development is intended for non-residential use.</t>
+        </is>
+      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Surface water disposal[]</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr"/>
+          <t>Hours of operation[]</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
       <c r="E84" s="2" t="inlineStr"/>
       <c r="F84" s="2" t="inlineStr"/>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Method for disposing of surface water</t>
+          <t>A use class or type of use</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -3202,16 +3210,8 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>Hours of operation</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>Proposed operating hours if the proposed development is intended for non-residential use.</t>
-        </is>
-      </c>
+      <c r="A85" s="2" t="n"/>
+      <c r="B85" s="2" t="n"/>
       <c r="C85" s="2" t="inlineStr">
         <is>
           <t>Hours of operation[]</t>
@@ -3219,24 +3219,24 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Use</t>
+          <t>Use other</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr"/>
       <c r="F85" s="2" t="inlineStr"/>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>A use class or type of use</t>
+          <t>Specify use if use is "other"</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3250,24 +3250,28 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Use other</t>
-        </is>
-      </c>
-      <c r="E86" s="2" t="inlineStr"/>
+          <t>Operational times[]</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>Day type</t>
+        </is>
+      </c>
       <c r="F86" s="2" t="inlineStr"/>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Specify use if use is "other"</t>
+          <t>Day or type of day</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3286,23 +3290,23 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Day type</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr"/>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Day or type of day</t>
+          <t>True or False - explicitly state when closed</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3321,23 +3325,27 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="F88" s="2" t="inlineStr"/>
+          <t>Time ranges[]</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>Open time</t>
+        </is>
+      </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>True or False - explicitly state when closed</t>
+          <t>Opening time</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3361,12 +3369,12 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>Open time</t>
+          <t>Close time</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Opening time</t>
+          <t>Closing time</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -3390,88 +3398,80 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Operational times[]</t>
-        </is>
-      </c>
-      <c r="E90" s="2" t="inlineStr">
-        <is>
-          <t>Time ranges[]</t>
-        </is>
-      </c>
-      <c r="F90" s="2" t="inlineStr">
-        <is>
-          <t>Close time</t>
-        </is>
-      </c>
+          <t>Hours not known</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr"/>
+      <c r="F90" s="2" t="inlineStr"/>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Closing time</t>
+          <t>Applicant states they do not know the hours of operation</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n"/>
-      <c r="B91" s="2" t="n"/>
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>Non residential floorspace</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>Details of changes to non-residential floorspace in the proposed development.</t>
+        </is>
+      </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Hours of operation[]</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>Hours not known</t>
-        </is>
-      </c>
+          <t>Non residential change</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr"/>
       <c r="E91" s="2" t="inlineStr"/>
       <c r="F91" s="2" t="inlineStr"/>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Applicant states they do not know the hours of operation</t>
+          <t>Does the proposal involve the loss, gain, or change of non-residential floorspace?</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>Non residential floorspace</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>Details of changes to non-residential floorspace in the proposed development.</t>
-        </is>
-      </c>
+      <c r="A92" s="2" t="n"/>
+      <c r="B92" s="2" t="n"/>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Non residential change</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr"/>
+          <t>Floorspace details[]</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
       <c r="E92" s="2" t="inlineStr"/>
       <c r="F92" s="2" t="inlineStr"/>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Does the proposal involve the loss, gain, or change of non-residential floorspace?</t>
+          <t>A use class or type of use</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -3495,24 +3495,24 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Use</t>
+          <t>Specified use</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr"/>
       <c r="F93" s="2" t="inlineStr"/>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>A use class or type of use</t>
+          <t>A specified use if no applicable use class is available</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3526,19 +3526,19 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Specified use</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr"/>
       <c r="F94" s="2" t="inlineStr"/>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>A specified use if no applicable use class is available</t>
+          <t>Whether the facility is not applicable</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
@@ -3557,24 +3557,24 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Existing gross floorspace</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr"/>
       <c r="F95" s="2" t="inlineStr"/>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>Whether the facility is not applicable</t>
+          <t>Existing gross internal floorspace, in sqm</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3588,24 +3588,24 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Existing gross floorspace</t>
+          <t>Is floorspace lost known</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr"/>
       <c r="F96" s="2" t="inlineStr"/>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Existing gross internal floorspace, in sqm</t>
+          <t>Whether the amount of floorspace to be lost is known</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3619,19 +3619,19 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Is floorspace lost known</t>
+          <t>Floorspace lost</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr"/>
       <c r="F97" s="2" t="inlineStr"/>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>Whether the amount of floorspace to be lost is known</t>
+          <t>Gross floorspace to be lost by change of use, in sqm</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
@@ -3650,19 +3650,19 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Floorspace lost</t>
+          <t>Is total gross proposed known</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr"/>
       <c r="F98" s="2" t="inlineStr"/>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Gross floorspace to be lost by change of use, in sqm</t>
+          <t>Whether the total gross proposed floorspace is known</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
@@ -3681,19 +3681,19 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Is total gross proposed known</t>
+          <t>Total gross proposed</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr"/>
       <c r="F99" s="2" t="inlineStr"/>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Whether the total gross proposed floorspace is known</t>
+          <t>Total gross internal floorspace proposed, in sqm</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
@@ -3712,14 +3712,14 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Total gross proposed</t>
+          <t>Net additional floorspace</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr"/>
       <c r="F100" s="2" t="inlineStr"/>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Total gross internal floorspace proposed, in sqm</t>
+          <t>Net additional gross internal floorspace, in sqm</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3738,24 +3738,24 @@
       <c r="B101" s="2" t="n"/>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Floorspace details[]</t>
+          <t>Room details[]</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Net additional floorspace</t>
+          <t>Use class for accommodation</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr"/>
       <c r="F101" s="2" t="inlineStr"/>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Net additional gross internal floorspace, in sqm</t>
+          <t>Type of non-residential use class referring to accommodation uses</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
@@ -3774,24 +3774,24 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Use class for accommodation</t>
+          <t>Use other</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr"/>
       <c r="F102" s="2" t="inlineStr"/>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>Type of non-residential use class referring to accommodation uses</t>
+          <t>Specify use if use is "other"</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3805,19 +3805,19 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Use other</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr"/>
       <c r="F103" s="2" t="inlineStr"/>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>Specify use if use is "other"</t>
+          <t>Used to explicitly state the use class does not apply to the proposal</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
@@ -3836,14 +3836,14 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Is existing rooms lost known</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr"/>
       <c r="F104" s="2" t="inlineStr"/>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>Used to explicitly state the use class does not apply to the proposal</t>
+          <t>Whether the total existing rooms that will be lost is known</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -3867,19 +3867,19 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Is existing rooms lost known</t>
+          <t>Existing rooms lost</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr"/>
       <c r="F105" s="2" t="inlineStr"/>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>Whether the total existing rooms that will be lost is known</t>
+          <t>Existing rooms to be lost by change of use</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
@@ -3898,19 +3898,19 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Existing rooms lost</t>
+          <t>Is total rooms proposed known</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr"/>
       <c r="F106" s="2" t="inlineStr"/>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Existing rooms to be lost by change of use</t>
+          <t>Whether the total rooms proposed is known</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
@@ -3929,19 +3929,19 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Is total rooms proposed known</t>
+          <t>Total rooms proposed</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr"/>
       <c r="F107" s="2" t="inlineStr"/>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Whether the total rooms proposed is known</t>
+          <t>Total rooms proposed (including change of use)</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
@@ -3960,14 +3960,14 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Total rooms proposed</t>
+          <t>Net additional rooms</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr"/>
       <c r="F108" s="2" t="inlineStr"/>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Total rooms proposed (including change of use)</t>
+          <t>Net additional rooms following development</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -3977,33 +3977,37 @@
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="n"/>
-      <c r="B109" s="2" t="n"/>
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>Ownership certificates and agricultural land declaration</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
+        </is>
+      </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Room details[]</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
-        <is>
-          <t>Net additional rooms</t>
-        </is>
-      </c>
+          <t>Sole owner</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr"/>
       <c r="E109" s="2" t="inlineStr"/>
       <c r="F109" s="2" t="inlineStr"/>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>Net additional rooms following development</t>
+          <t>Is the applicant the sole owner of the land?</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
@@ -4013,19 +4017,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>Ownership certificates and agricultural land declaration</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
-        </is>
-      </c>
+      <c r="A110" s="2" t="n"/>
+      <c r="B110" s="2" t="n"/>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Sole owner</t>
+          <t>Agricultural tenants</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr"/>
@@ -4033,7 +4029,7 @@
       <c r="F110" s="2" t="inlineStr"/>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>Is the applicant the sole owner of the land?</t>
+          <t>Are there any agricultural tenants on the land?</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -4052,25 +4048,33 @@
       <c r="B111" s="2" t="n"/>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Agricultural tenants</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr"/>
-      <c r="E111" s="2" t="inlineStr"/>
+          <t>Owners and tenants[]</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
       <c r="F111" s="2" t="inlineStr"/>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>Are there any agricultural tenants on the land?</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4089,13 +4093,13 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr"/>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -4105,7 +4109,7 @@
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4124,13 +4128,13 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr"/>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -4159,13 +4163,13 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr"/>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -4194,13 +4198,13 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr"/>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -4210,7 +4214,7 @@
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4224,23 +4228,19 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E116" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Notice date</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr"/>
       <c r="F116" s="2" t="inlineStr"/>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Date when notice was served</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
@@ -4254,24 +4254,20 @@
       <c r="B117" s="2" t="n"/>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Owners and tenants[]</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
-        <is>
-          <t>Notice date</t>
-        </is>
-      </c>
+          <t>Steps taken</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr"/>
       <c r="E117" s="2" t="inlineStr"/>
       <c r="F117" s="2" t="inlineStr"/>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>Date when notice was served</t>
+          <t>Description of steps taken to identify unknown owners or tenants</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr">
@@ -4285,15 +4281,19 @@
       <c r="B118" s="2" t="n"/>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Steps taken</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr"/>
+          <t>Newspaper notices[]</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Newspaper name</t>
+        </is>
+      </c>
       <c r="E118" s="2" t="inlineStr"/>
       <c r="F118" s="2" t="inlineStr"/>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>Description of steps taken to identify unknown owners or tenants</t>
+          <t>Name of the newspaper where notice was published</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -4303,7 +4303,7 @@
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4317,19 +4317,19 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Newspaper name</t>
+          <t>Publication date</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr"/>
       <c r="F119" s="2" t="inlineStr"/>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>Name of the newspaper where notice was published</t>
+          <t>Date when the notice was published</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr">
@@ -4343,29 +4343,25 @@
       <c r="B120" s="2" t="n"/>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Newspaper notices[]</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
-        <is>
-          <t>Publication date</t>
-        </is>
-      </c>
+          <t>Ownership certificate type</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr"/>
       <c r="E120" s="2" t="inlineStr"/>
       <c r="F120" s="2" t="inlineStr"/>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Date when the notice was published</t>
+          <t>The type of ownership certificate based on ownership and tenancy status</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4370,7 @@
       <c r="B121" s="2" t="n"/>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Ownership certificate type</t>
+          <t>Applicant signature</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr"/>
@@ -4382,12 +4378,12 @@
       <c r="F121" s="2" t="inlineStr"/>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>The type of ownership certificate based on ownership and tenancy status</t>
+          <t>Digital signature of the applicant</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr">
@@ -4401,7 +4397,7 @@
       <c r="B122" s="2" t="n"/>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Applicant signature</t>
+          <t>Agent signature</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr"/>
@@ -4409,7 +4405,7 @@
       <c r="F122" s="2" t="inlineStr"/>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>Digital signature of the applicant</t>
+          <t>Digital signature of the agent (if applicable)</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -4428,7 +4424,7 @@
       <c r="B123" s="2" t="n"/>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>Agent signature</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr"/>
@@ -4436,7 +4432,7 @@
       <c r="F123" s="2" t="inlineStr"/>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>Digital signature of the agent (if applicable)</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
@@ -4451,11 +4447,19 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="n"/>
-      <c r="B124" s="2" t="n"/>
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>Pre-application advice</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>Details of pre-application advice previously received from the planning authority</t>
+        </is>
+      </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Pre-application advice sought</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr"/>
@@ -4463,34 +4467,26 @@
       <c r="F124" s="2" t="inlineStr"/>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Whether pre-application advice has been sought from the planning authority</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="inlineStr">
-        <is>
-          <t>Pre-application advice</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
-        </is>
-      </c>
+      <c r="A125" s="2" t="n"/>
+      <c r="B125" s="2" t="n"/>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Pre-application advice sought</t>
+          <t>Officer name</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr"/>
@@ -4498,17 +4494,17 @@
       <c r="F125" s="2" t="inlineStr"/>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Whether pre-application advice has been sought from the planning authority</t>
+          <t>Name of the planning officer who provided the pre-application advice</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4517,7 +4513,7 @@
       <c r="B126" s="2" t="n"/>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Officer name</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr"/>
@@ -4525,7 +4521,7 @@
       <c r="F126" s="2" t="inlineStr"/>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>Name of the planning officer who provided the pre-application advice</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
@@ -4544,7 +4540,7 @@
       <c r="B127" s="2" t="n"/>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Advice date</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr"/>
@@ -4552,7 +4548,7 @@
       <c r="F127" s="2" t="inlineStr"/>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -4571,7 +4567,7 @@
       <c r="B128" s="2" t="n"/>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Advice date</t>
+          <t>Advice summary</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr"/>
@@ -4579,7 +4575,7 @@
       <c r="F128" s="2" t="inlineStr"/>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
+          <t>Summary of the pre-application advice received from the planning authority</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
@@ -4594,11 +4590,19 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="n"/>
-      <c r="B129" s="2" t="n"/>
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>Processes machinery waste</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>How waste will be managed on the site</t>
+        </is>
+      </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Advice summary</t>
+          <t>Site activity details</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr"/>
@@ -4606,7 +4610,7 @@
       <c r="F129" s="2" t="inlineStr"/>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>Summary of the pre-application advice received from the planning authority</t>
+          <t>Description of activities, processes, and end products including site operations, plant, ventilation, and machinery</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
@@ -4616,24 +4620,16 @@
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="inlineStr">
-        <is>
-          <t>Processes machinery waste</t>
-        </is>
-      </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>How waste will be managed on the site</t>
-        </is>
-      </c>
+      <c r="A130" s="2" t="n"/>
+      <c r="B130" s="2" t="n"/>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Site activity details</t>
+          <t>Proposal waste management</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr"/>
@@ -4641,12 +4637,12 @@
       <c r="F130" s="2" t="inlineStr"/>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>Description of activities, processes, and end products including site operations, plant, ventilation, and machinery</t>
+          <t>Whether the proposal involves waste management development</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
@@ -4660,20 +4656,24 @@
       <c r="B131" s="2" t="n"/>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>Proposal waste management</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr"/>
+          <t>Waste management[]</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>Waste management facility type</t>
+        </is>
+      </c>
       <c r="E131" s="2" t="inlineStr"/>
       <c r="F131" s="2" t="inlineStr"/>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>Whether the proposal involves waste management development</t>
+          <t>Type of waste management facility</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I131" s="2" t="inlineStr">
@@ -4692,24 +4692,24 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Waste management facility type</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr"/>
       <c r="F132" s="2" t="inlineStr"/>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>Type of waste management facility</t>
+          <t>Whether the facility is not applicable</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4723,19 +4723,19 @@
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Total capacity</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr"/>
       <c r="F133" s="2" t="inlineStr"/>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>Whether the facility is not applicable</t>
+          <t>Total capacity of void in cubic metres (or tonnes/litres)</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I133" s="2" t="inlineStr">
@@ -4754,19 +4754,19 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Total capacity</t>
+          <t>Unit type</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr"/>
       <c r="F134" s="2" t="inlineStr"/>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>Total capacity of void in cubic metres (or tonnes/litres)</t>
+          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr">
@@ -4785,19 +4785,19 @@
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>Unit type</t>
+          <t>Annual throughput</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr"/>
       <c r="F135" s="2" t="inlineStr"/>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
+          <t>Maximum annual operational throughput in tonnes/litres</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I135" s="2" t="inlineStr">
@@ -4816,19 +4816,19 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>Annual throughput</t>
+          <t>Unit type</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr"/>
       <c r="F136" s="2" t="inlineStr"/>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>Maximum annual operational throughput in tonnes/litres</t>
+          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr">
@@ -4842,24 +4842,24 @@
       <c r="B137" s="2" t="n"/>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>Waste management[]</t>
+          <t>Waste streams throughput</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>Unit type</t>
+          <t>Municipal</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr"/>
       <c r="F137" s="2" t="inlineStr"/>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
+          <t>Maximum throughput for municipal waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I137" s="2" t="inlineStr">
@@ -4878,14 +4878,14 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Municipal</t>
+          <t>Construction demolition</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr"/>
       <c r="F138" s="2" t="inlineStr"/>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for municipal waste (annual throughput in tonnes/litres)</t>
+          <t>Maximum throughput for construction and demolition waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -4909,14 +4909,14 @@
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>Construction demolition</t>
+          <t>Commercial industrial</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr"/>
       <c r="F139" s="2" t="inlineStr"/>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for construction and demolition waste (annual throughput in tonnes/litres)</t>
+          <t>Maximum throughput for commercial and industrial waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -4940,14 +4940,14 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>Commercial industrial</t>
+          <t>Hazardous</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr"/>
       <c r="F140" s="2" t="inlineStr"/>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for commercial and industrial waste (annual throughput in tonnes/litres)</t>
+          <t>Maximum throughput for hazardous waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -4962,50 +4962,46 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="2" t="n"/>
-      <c r="B141" s="2" t="n"/>
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>Description of the proposal</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>What development, works or change of use is proposed</t>
+        </is>
+      </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>Waste streams throughput</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
-        <is>
-          <t>Hazardous</t>
-        </is>
-      </c>
+          <t>Proposal description</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr"/>
       <c r="E141" s="2" t="inlineStr"/>
       <c r="F141" s="2" t="inlineStr"/>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for hazardous waste (annual throughput in tonnes/litres)</t>
+          <t>A description of what is being proposed, including the development, works, or change of use</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="inlineStr">
-        <is>
-          <t>Description of the proposal</t>
-        </is>
-      </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>What development, works or change of use is proposed</t>
-        </is>
-      </c>
+      <c r="A142" s="2" t="n"/>
+      <c r="B142" s="2" t="n"/>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Proposal description</t>
+          <t>Reserved matters[]</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr"/>
@@ -5013,12 +5009,12 @@
       <c r="F142" s="2" t="inlineStr"/>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>A description of what is being proposed, including the development, works, or change of use</t>
+          <t>Identifies which reserved matters are being submitted for approval as part of this application</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I142" s="2" t="inlineStr">
@@ -5032,7 +5028,7 @@
       <c r="B143" s="2" t="n"/>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>Reserved matters[]</t>
+          <t>Proposal started</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr"/>
@@ -5040,12 +5036,12 @@
       <c r="F143" s="2" t="inlineStr"/>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>Identifies which reserved matters are being submitted for approval as part of this application</t>
+          <t>Has any work on the proposal already been started</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I143" s="2" t="inlineStr">
@@ -5059,7 +5055,7 @@
       <c r="B144" s="2" t="n"/>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Proposal started</t>
+          <t>Proposal start date</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr"/>
@@ -5067,17 +5063,17 @@
       <c r="F144" s="2" t="inlineStr"/>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been started</t>
+          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5086,7 +5082,7 @@
       <c r="B145" s="2" t="n"/>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>Proposal start date</t>
+          <t>Proposal completed</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr"/>
@@ -5094,17 +5090,17 @@
       <c r="F145" s="2" t="inlineStr"/>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
+          <t>Has any work on the proposal already been completed</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5113,7 +5109,7 @@
       <c r="B146" s="2" t="n"/>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Proposal completed</t>
+          <t>Proposal completion date</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr"/>
@@ -5121,26 +5117,34 @@
       <c r="F146" s="2" t="inlineStr"/>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been completed</t>
+          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="2" t="n"/>
-      <c r="B147" s="2" t="n"/>
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>Residential units</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>Details of the residential units that make up both the current and proposed development.</t>
+        </is>
+      </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>Proposal completion date</t>
+          <t>Residential unit change</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr"/>
@@ -5148,47 +5152,43 @@
       <c r="F147" s="2" t="inlineStr"/>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
+          <t>Proposal includes the gain, loss or change of use of residential units</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="inlineStr">
-        <is>
-          <t>Residential units</t>
-        </is>
-      </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>Details of the residential units that make up both the current and proposed development.</t>
-        </is>
-      </c>
+      <c r="A148" s="2" t="n"/>
+      <c r="B148" s="2" t="n"/>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Residential unit change</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr"/>
+          <t>Residential unit summary[]</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Tenure type</t>
+        </is>
+      </c>
       <c r="E148" s="2" t="inlineStr"/>
       <c r="F148" s="2" t="inlineStr"/>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>Proposal includes the gain, loss or change of use of residential units</t>
+          <t>Category of housing tenure</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I148" s="2" t="inlineStr">
@@ -5207,14 +5207,14 @@
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>Tenure type</t>
+          <t>Housing type</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr"/>
       <c r="F149" s="2" t="inlineStr"/>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>Category of housing tenure</t>
+          <t>Type of housing</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
@@ -5238,19 +5238,23 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>Housing type</t>
-        </is>
-      </c>
-      <c r="E150" s="2" t="inlineStr"/>
+          <t>Existing unit breakdown[]</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>Units unknown</t>
+        </is>
+      </c>
       <c r="F150" s="2" t="inlineStr"/>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>Type of housing</t>
+          <t>Whether the number of units is unknown</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
@@ -5274,13 +5278,17 @@
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>Units unknown</t>
-        </is>
-      </c>
-      <c r="F151" s="2" t="inlineStr"/>
+          <t>Units per bedroom number[]</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>No bedrooms unknown</t>
+        </is>
+      </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>Whether the number of units is unknown</t>
+          <t>Set to true when counting units where bedroom number is unknown</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -5314,22 +5322,22 @@
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>No bedrooms unknown</t>
+          <t>Number of bedrooms</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>Set to true when counting units where bedroom number is unknown</t>
+          <t>The number of bedrooms in unit</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5353,12 +5361,12 @@
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>Number of bedrooms</t>
+          <t>Units</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>The number of bedrooms in unit</t>
+          <t>The number of units of that bedroom count</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
@@ -5368,7 +5376,7 @@
       </c>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5387,17 +5395,13 @@
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>Units per bedroom number[]</t>
-        </is>
-      </c>
-      <c r="F154" s="2" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
+          <t>Total units</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr"/>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>The number of units of that bedroom count</t>
+          <t>Total number of units</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
@@ -5407,7 +5411,7 @@
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5421,28 +5425,28 @@
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>Existing unit breakdown[]</t>
+          <t>Proposed unit breakdown[]</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>Total units</t>
+          <t>Units unknown</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr"/>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Total number of units</t>
+          <t>Whether the number of units is unknown</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I155" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5461,13 +5465,17 @@
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>Units unknown</t>
-        </is>
-      </c>
-      <c r="F156" s="2" t="inlineStr"/>
+          <t>Units per bedroom number[]</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>No bedrooms unknown</t>
+        </is>
+      </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Whether the number of units is unknown</t>
+          <t>Set to true when counting units where bedroom number is unknown</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -5501,22 +5509,22 @@
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>No bedrooms unknown</t>
+          <t>Number of bedrooms</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Set to true when counting units where bedroom number is unknown</t>
+          <t>The number of bedrooms in unit</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I157" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5548,12 @@
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>Number of bedrooms</t>
+          <t>Units</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>The number of bedrooms in unit</t>
+          <t>The number of units of that bedroom count</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
@@ -5555,7 +5563,7 @@
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5574,17 +5582,13 @@
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>Units per bedroom number[]</t>
-        </is>
-      </c>
-      <c r="F159" s="2" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
+          <t>Total units</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr"/>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>The number of units of that bedroom count</t>
+          <t>Total number of units</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -5594,7 +5598,7 @@
       </c>
       <c r="I159" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5603,23 +5607,15 @@
       <c r="B160" s="2" t="n"/>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Residential unit summary[]</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
-        <is>
-          <t>Proposed unit breakdown[]</t>
-        </is>
-      </c>
-      <c r="E160" s="2" t="inlineStr">
-        <is>
-          <t>Total units</t>
-        </is>
-      </c>
+          <t>Total existing units</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr"/>
+      <c r="E160" s="2" t="inlineStr"/>
       <c r="F160" s="2" t="inlineStr"/>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>Total number of units</t>
+          <t>The total number of existing units</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
@@ -5629,7 +5625,7 @@
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5638,7 +5634,7 @@
       <c r="B161" s="2" t="n"/>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>Total existing units</t>
+          <t>Total proposed units</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr"/>
@@ -5646,7 +5642,7 @@
       <c r="F161" s="2" t="inlineStr"/>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>The total number of existing units</t>
+          <t>The total number of proposed units</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
@@ -5665,7 +5661,7 @@
       <c r="B162" s="2" t="n"/>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>Total proposed units</t>
+          <t>Net change</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr"/>
@@ -5673,7 +5669,7 @@
       <c r="F162" s="2" t="inlineStr"/>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>The total number of proposed units</t>
+          <t>Calculated net change in units</t>
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr">
@@ -5688,11 +5684,19 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="2" t="n"/>
-      <c r="B163" s="2" t="n"/>
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>Site area</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>How big the site is including relevant measurements</t>
+        </is>
+      </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>Net change</t>
+          <t>Site area in hectares</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr"/>
@@ -5700,7 +5704,7 @@
       <c r="F163" s="2" t="inlineStr"/>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>Calculated net change in units</t>
+          <t>The size of the site in hectares</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr">
@@ -5715,19 +5719,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="2" t="inlineStr">
-        <is>
-          <t>Site area</t>
-        </is>
-      </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>How big the site is including relevant measurements</t>
-        </is>
-      </c>
+      <c r="A164" s="2" t="n"/>
+      <c r="B164" s="2" t="n"/>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>Site area in hectares</t>
+          <t>Site area provided by</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr"/>
@@ -5735,39 +5731,51 @@
       <c r="F164" s="2" t="inlineStr"/>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>The size of the site in hectares</t>
+          <t>Who provided the site area value</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="n"/>
-      <c r="B165" s="2" t="n"/>
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>Site details</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>Where the proposed development will be built.</t>
+        </is>
+      </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>Site area provided by</t>
-        </is>
-      </c>
-      <c r="D165" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>Site boundary</t>
+        </is>
+      </c>
       <c r="E165" s="2" t="inlineStr"/>
       <c r="F165" s="2" t="inlineStr"/>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>Who provided the site area value</t>
+          <t>Geometry of the site of the development, typically in GeoJSON format</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>wkt</t>
         </is>
       </c>
       <c r="I165" s="2" t="inlineStr">
@@ -5777,16 +5785,8 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="inlineStr">
-        <is>
-          <t>Site details</t>
-        </is>
-      </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>Where the proposed development will be built.</t>
-        </is>
-      </c>
+      <c r="A166" s="2" t="n"/>
+      <c r="B166" s="2" t="n"/>
       <c r="C166" s="2" t="inlineStr">
         <is>
           <t>Site locations[]</t>
@@ -5794,19 +5794,19 @@
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>Site boundary</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr"/>
       <c r="F166" s="2" t="inlineStr"/>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>Geometry of the site of the development, typically in GeoJSON format</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t>wkt</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I166" s="2" t="inlineStr">
@@ -5825,14 +5825,14 @@
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr"/>
       <c r="F167" s="2" t="inlineStr"/>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -5856,19 +5856,19 @@
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Easting</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr"/>
       <c r="F168" s="2" t="inlineStr"/>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I168" s="2" t="inlineStr">
@@ -5887,14 +5887,14 @@
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>Easting</t>
+          <t>Northing</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr"/>
       <c r="F169" s="2" t="inlineStr"/>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
+          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
@@ -5918,14 +5918,14 @@
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>Northing</t>
+          <t>Latitude</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr"/>
       <c r="F170" s="2" t="inlineStr"/>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
+          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
@@ -5949,14 +5949,14 @@
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>Latitude</t>
+          <t>Longitude</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr"/>
       <c r="F171" s="2" t="inlineStr"/>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
@@ -5980,19 +5980,19 @@
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>Longitude</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr"/>
       <c r="F172" s="2" t="inlineStr"/>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>A text description providing details about the subject. For parking changes, this describes how the proposed works affect existing car parking arrangements.</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I172" s="2" t="inlineStr">
@@ -6011,14 +6011,14 @@
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>UPRNs[]</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr"/>
       <c r="F173" s="2" t="inlineStr"/>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>A text description providing details about the subject. For parking changes, this describes how the proposed works affect existing car parking arrangements.</t>
+          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
@@ -6033,50 +6033,46 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="2" t="n"/>
-      <c r="B174" s="2" t="n"/>
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>Site Visit Details</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>Information to help the planning authority arrange a site visit</t>
+        </is>
+      </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="D174" s="2" t="inlineStr">
-        <is>
-          <t>UPRNs[]</t>
-        </is>
-      </c>
+          <t>Site seen from public area</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr"/>
       <c r="E174" s="2" t="inlineStr"/>
       <c r="F174" s="2" t="inlineStr"/>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
+          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I174" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="2" t="inlineStr">
-        <is>
-          <t>Site Visit Details</t>
-        </is>
-      </c>
-      <c r="B175" s="2" t="inlineStr">
-        <is>
-          <t>Information to help the planning authority arrange a site visit</t>
-        </is>
-      </c>
+      <c r="A175" s="2" t="n"/>
+      <c r="B175" s="2" t="n"/>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>Site seen from public area</t>
+          <t>Site visit contact type</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr"/>
@@ -6084,12 +6080,12 @@
       <c r="F175" s="2" t="inlineStr"/>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
+          <t>Indicates who the authority should contact to arrange a site visit</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I175" s="2" t="inlineStr">
@@ -6103,7 +6099,7 @@
       <c r="B176" s="2" t="n"/>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>Site visit contact type</t>
+          <t>Contact reference</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr"/>
@@ -6111,17 +6107,17 @@
       <c r="F176" s="2" t="inlineStr"/>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>Indicates who the authority should contact to arrange a site visit</t>
+          <t>The reference of the applicant or agent who should be contacted for site visits</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I176" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -6130,15 +6126,19 @@
       <c r="B177" s="2" t="n"/>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>Contact reference</t>
-        </is>
-      </c>
-      <c r="D177" s="2" t="inlineStr"/>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>Full name</t>
+        </is>
+      </c>
       <c r="E177" s="2" t="inlineStr"/>
       <c r="F177" s="2" t="inlineStr"/>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+          <t>The complete name of a person</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="I177" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -6162,14 +6162,14 @@
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>Full name</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr"/>
       <c r="F178" s="2" t="inlineStr"/>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>The complete name of a person</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr">
@@ -6193,14 +6193,14 @@
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr"/>
       <c r="F179" s="2" t="inlineStr"/>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="H179" s="2" t="inlineStr">
@@ -6209,37 +6209,6 @@
         </is>
       </c>
       <c r="I179" s="2" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" s="2" t="n"/>
-      <c r="B180" s="2" t="n"/>
-      <c r="C180" s="2" t="inlineStr">
-        <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="D180" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="E180" s="2" t="inlineStr"/>
-      <c r="F180" s="2" t="inlineStr"/>
-      <c r="G180" s="2" t="inlineStr">
-        <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
-        </is>
-      </c>
-      <c r="H180" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="I180" s="2" t="inlineStr">
         <is>
           <t>MUST</t>
         </is>
@@ -6247,50 +6216,50 @@
     </row>
   </sheetData>
   <mergeCells count="44">
-    <mergeCell ref="A57:A59"/>
-    <mergeCell ref="A110:A124"/>
-    <mergeCell ref="A42:A55"/>
-    <mergeCell ref="A2:A19"/>
-    <mergeCell ref="A24:A31"/>
-    <mergeCell ref="A36:A41"/>
-    <mergeCell ref="A130:A141"/>
-    <mergeCell ref="A125:A129"/>
-    <mergeCell ref="A79:A84"/>
-    <mergeCell ref="B166:B174"/>
-    <mergeCell ref="B92:B109"/>
-    <mergeCell ref="A85:A91"/>
-    <mergeCell ref="A164:A165"/>
-    <mergeCell ref="A69:A78"/>
-    <mergeCell ref="B130:B141"/>
-    <mergeCell ref="B63:B68"/>
-    <mergeCell ref="B125:B129"/>
-    <mergeCell ref="A32:A35"/>
-    <mergeCell ref="B175:B180"/>
-    <mergeCell ref="B56"/>
-    <mergeCell ref="A148:A163"/>
-    <mergeCell ref="A92:A109"/>
-    <mergeCell ref="A60:A62"/>
-    <mergeCell ref="A20:A23"/>
-    <mergeCell ref="B85:B91"/>
-    <mergeCell ref="A142:A147"/>
-    <mergeCell ref="B164:B165"/>
-    <mergeCell ref="A175:A180"/>
-    <mergeCell ref="B69:B78"/>
-    <mergeCell ref="B142:B147"/>
-    <mergeCell ref="B36:B41"/>
-    <mergeCell ref="A56"/>
-    <mergeCell ref="B57:B59"/>
-    <mergeCell ref="B110:B124"/>
-    <mergeCell ref="A166:A174"/>
-    <mergeCell ref="B20:B23"/>
-    <mergeCell ref="B42:B55"/>
-    <mergeCell ref="B148:B163"/>
-    <mergeCell ref="B60:B62"/>
-    <mergeCell ref="A63:A68"/>
-    <mergeCell ref="B2:B19"/>
-    <mergeCell ref="B24:B31"/>
-    <mergeCell ref="B32:B35"/>
-    <mergeCell ref="B79:B84"/>
+    <mergeCell ref="B35:B40"/>
+    <mergeCell ref="A68:A77"/>
+    <mergeCell ref="B141:B146"/>
+    <mergeCell ref="B31:B34"/>
+    <mergeCell ref="B147:B162"/>
+    <mergeCell ref="B109:B123"/>
+    <mergeCell ref="B55"/>
+    <mergeCell ref="B129:B140"/>
+    <mergeCell ref="A147:A162"/>
+    <mergeCell ref="B124:B128"/>
+    <mergeCell ref="B84:B90"/>
+    <mergeCell ref="B2:B18"/>
+    <mergeCell ref="A59:A61"/>
+    <mergeCell ref="B62:B67"/>
+    <mergeCell ref="A78:A83"/>
+    <mergeCell ref="A91:A108"/>
+    <mergeCell ref="A174:A179"/>
+    <mergeCell ref="B56:B58"/>
+    <mergeCell ref="B41:B54"/>
+    <mergeCell ref="B19:B22"/>
+    <mergeCell ref="B59:B61"/>
+    <mergeCell ref="B23:B30"/>
+    <mergeCell ref="A163:A164"/>
+    <mergeCell ref="B78:B83"/>
+    <mergeCell ref="A165:A173"/>
+    <mergeCell ref="B91:B108"/>
+    <mergeCell ref="A2:A18"/>
+    <mergeCell ref="B174:B179"/>
+    <mergeCell ref="A109:A123"/>
+    <mergeCell ref="A19:A22"/>
+    <mergeCell ref="A141:A146"/>
+    <mergeCell ref="A35:A40"/>
+    <mergeCell ref="A124:A128"/>
+    <mergeCell ref="B163:B164"/>
+    <mergeCell ref="A84:A90"/>
+    <mergeCell ref="A31:A34"/>
+    <mergeCell ref="A55"/>
+    <mergeCell ref="A41:A54"/>
+    <mergeCell ref="B165:B173"/>
+    <mergeCell ref="B68:B77"/>
+    <mergeCell ref="A23:A30"/>
+    <mergeCell ref="A129:A140"/>
+    <mergeCell ref="A56:A58"/>
+    <mergeCell ref="A62:A67"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/generated/spreadsheet/outline-planning-outline.xlsx
+++ b/generated/spreadsheet/outline-planning-outline.xlsx
@@ -3255,13 +3255,13 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Day type</t>
+          <t>Schedule days[]</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr"/>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Day or type of day</t>
+          <t>List of days or day categories that a schedule entry applies to</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">

--- a/generated/spreadsheet/outline-planning-outline.xlsx
+++ b/generated/spreadsheet/outline-planning-outline.xlsx
@@ -2507,7 +2507,7 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr">
@@ -4553,7 +4553,7 @@
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I127" s="2" t="inlineStr">

--- a/generated/spreadsheet/outline-planning-outline.xlsx
+++ b/generated/spreadsheet/outline-planning-outline.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I179"/>
+  <dimension ref="A1:I178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -4597,7 +4597,8 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>How waste will be managed on the site</t>
+          <t xml:space="preserve">How waste will be managed on the site
+</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -4637,7 +4638,7 @@
       <c r="F130" s="2" t="inlineStr"/>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>Whether the proposal involves waste management development</t>
+          <t>Whether the proposal involves any waste management facility that is relevant to the proposal</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
@@ -4668,7 +4669,7 @@
       <c r="F131" s="2" t="inlineStr"/>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>Type of waste management facility</t>
+          <t>Type of waste management facility being described in this entry</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
@@ -4692,24 +4693,24 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Total capacity</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr"/>
       <c r="F132" s="2" t="inlineStr"/>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>Whether the facility is not applicable</t>
+          <t>Total capacity of void in cubic metres (or tonnes/litres)</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4723,24 +4724,24 @@
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>Total capacity</t>
+          <t>Unit type</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr"/>
       <c r="F133" s="2" t="inlineStr"/>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>Total capacity of void in cubic metres (or tonnes/litres)</t>
+          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4754,24 +4755,24 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Unit type</t>
+          <t>Annual throughput</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr"/>
       <c r="F134" s="2" t="inlineStr"/>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
+          <t>Maximum annual operational throughput in tonnes/litres</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4785,24 +4786,24 @@
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>Annual throughput</t>
+          <t>Unit type</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr"/>
       <c r="F135" s="2" t="inlineStr"/>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>Maximum annual operational throughput in tonnes/litres</t>
+          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4811,24 +4812,24 @@
       <c r="B136" s="2" t="n"/>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Waste management[]</t>
+          <t>Waste streams throughput</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>Unit type</t>
+          <t>Municipal</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr"/>
       <c r="F136" s="2" t="inlineStr"/>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
+          <t>Maximum throughput for municipal waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr">
@@ -4847,14 +4848,14 @@
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>Municipal</t>
+          <t>Construction demolition</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr"/>
       <c r="F137" s="2" t="inlineStr"/>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for municipal waste (annual throughput in tonnes/litres)</t>
+          <t>Maximum throughput for construction and demolition waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -4878,14 +4879,14 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Construction demolition</t>
+          <t>Commercial industrial</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr"/>
       <c r="F138" s="2" t="inlineStr"/>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for construction and demolition waste (annual throughput in tonnes/litres)</t>
+          <t>Maximum throughput for commercial and industrial waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -4909,14 +4910,14 @@
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>Commercial industrial</t>
+          <t>Hazardous</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr"/>
       <c r="F139" s="2" t="inlineStr"/>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for commercial and industrial waste (annual throughput in tonnes/litres)</t>
+          <t>Maximum throughput for hazardous waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -4931,50 +4932,46 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="n"/>
-      <c r="B140" s="2" t="n"/>
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>Description of the proposal</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>What development, works or change of use is proposed</t>
+        </is>
+      </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Waste streams throughput</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
-        <is>
-          <t>Hazardous</t>
-        </is>
-      </c>
+          <t>Proposal description</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr"/>
       <c r="E140" s="2" t="inlineStr"/>
       <c r="F140" s="2" t="inlineStr"/>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for hazardous waste (annual throughput in tonnes/litres)</t>
+          <t>A description of what is being proposed, including the development, works, or change of use</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="2" t="inlineStr">
-        <is>
-          <t>Description of the proposal</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>What development, works or change of use is proposed</t>
-        </is>
-      </c>
+      <c r="A141" s="2" t="n"/>
+      <c r="B141" s="2" t="n"/>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>Proposal description</t>
+          <t>Reserved matters[]</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr"/>
@@ -4982,12 +4979,12 @@
       <c r="F141" s="2" t="inlineStr"/>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>A description of what is being proposed, including the development, works, or change of use</t>
+          <t>Identifies which reserved matters are being submitted for approval as part of this application</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I141" s="2" t="inlineStr">
@@ -5001,7 +4998,7 @@
       <c r="B142" s="2" t="n"/>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Reserved matters[]</t>
+          <t>Proposal started</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr"/>
@@ -5009,12 +5006,12 @@
       <c r="F142" s="2" t="inlineStr"/>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>Identifies which reserved matters are being submitted for approval as part of this application</t>
+          <t>Has any work on the proposal already been started</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I142" s="2" t="inlineStr">
@@ -5028,7 +5025,7 @@
       <c r="B143" s="2" t="n"/>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>Proposal started</t>
+          <t>Proposal start date</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr"/>
@@ -5036,17 +5033,17 @@
       <c r="F143" s="2" t="inlineStr"/>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been started</t>
+          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I143" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5055,7 +5052,7 @@
       <c r="B144" s="2" t="n"/>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Proposal start date</t>
+          <t>Proposal completed</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr"/>
@@ -5063,17 +5060,17 @@
       <c r="F144" s="2" t="inlineStr"/>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
+          <t>Has any work on the proposal already been completed</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5082,7 +5079,7 @@
       <c r="B145" s="2" t="n"/>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>Proposal completed</t>
+          <t>Proposal completion date</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr"/>
@@ -5090,26 +5087,34 @@
       <c r="F145" s="2" t="inlineStr"/>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been completed</t>
+          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="n"/>
-      <c r="B146" s="2" t="n"/>
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>Residential units</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>Details of the residential units that make up both the current and proposed development.</t>
+        </is>
+      </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Proposal completion date</t>
+          <t>Residential unit change</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr"/>
@@ -5117,47 +5122,43 @@
       <c r="F146" s="2" t="inlineStr"/>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
+          <t>Proposal includes the gain, loss or change of use of residential units</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="2" t="inlineStr">
-        <is>
-          <t>Residential units</t>
-        </is>
-      </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>Details of the residential units that make up both the current and proposed development.</t>
-        </is>
-      </c>
+      <c r="A147" s="2" t="n"/>
+      <c r="B147" s="2" t="n"/>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>Residential unit change</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr"/>
+          <t>Residential unit summary[]</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>Tenure type</t>
+        </is>
+      </c>
       <c r="E147" s="2" t="inlineStr"/>
       <c r="F147" s="2" t="inlineStr"/>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>Proposal includes the gain, loss or change of use of residential units</t>
+          <t>Category of housing tenure</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I147" s="2" t="inlineStr">
@@ -5176,14 +5177,14 @@
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>Tenure type</t>
+          <t>Housing type</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr"/>
       <c r="F148" s="2" t="inlineStr"/>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>Category of housing tenure</t>
+          <t>Type of housing</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -5207,19 +5208,23 @@
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>Housing type</t>
-        </is>
-      </c>
-      <c r="E149" s="2" t="inlineStr"/>
+          <t>Existing unit breakdown[]</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>Units unknown</t>
+        </is>
+      </c>
       <c r="F149" s="2" t="inlineStr"/>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>Type of housing</t>
+          <t>Whether the number of units is unknown</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I149" s="2" t="inlineStr">
@@ -5243,13 +5248,17 @@
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>Units unknown</t>
-        </is>
-      </c>
-      <c r="F150" s="2" t="inlineStr"/>
+          <t>Units per bedroom number[]</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>No bedrooms unknown</t>
+        </is>
+      </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>Whether the number of units is unknown</t>
+          <t>Set to true when counting units where bedroom number is unknown</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
@@ -5283,22 +5292,22 @@
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>No bedrooms unknown</t>
+          <t>Number of bedrooms</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>Set to true when counting units where bedroom number is unknown</t>
+          <t>The number of bedrooms in unit</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5322,12 +5331,12 @@
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>Number of bedrooms</t>
+          <t>Units</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>The number of bedrooms in unit</t>
+          <t>The number of units of that bedroom count</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr">
@@ -5337,7 +5346,7 @@
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5356,17 +5365,13 @@
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>Units per bedroom number[]</t>
-        </is>
-      </c>
-      <c r="F153" s="2" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
+          <t>Total units</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr"/>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>The number of units of that bedroom count</t>
+          <t>Total number of units</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
@@ -5376,7 +5381,7 @@
       </c>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5390,28 +5395,28 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>Existing unit breakdown[]</t>
+          <t>Proposed unit breakdown[]</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>Total units</t>
+          <t>Units unknown</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr"/>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>Total number of units</t>
+          <t>Whether the number of units is unknown</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5430,13 +5435,17 @@
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>Units unknown</t>
-        </is>
-      </c>
-      <c r="F155" s="2" t="inlineStr"/>
+          <t>Units per bedroom number[]</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>No bedrooms unknown</t>
+        </is>
+      </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Whether the number of units is unknown</t>
+          <t>Set to true when counting units where bedroom number is unknown</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -5470,22 +5479,22 @@
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>No bedrooms unknown</t>
+          <t>Number of bedrooms</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Set to true when counting units where bedroom number is unknown</t>
+          <t>The number of bedrooms in unit</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5518,12 @@
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>Number of bedrooms</t>
+          <t>Units</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>The number of bedrooms in unit</t>
+          <t>The number of units of that bedroom count</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -5524,7 +5533,7 @@
       </c>
       <c r="I157" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5543,17 +5552,13 @@
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>Units per bedroom number[]</t>
-        </is>
-      </c>
-      <c r="F158" s="2" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
+          <t>Total units</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr"/>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>The number of units of that bedroom count</t>
+          <t>Total number of units</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
@@ -5563,7 +5568,7 @@
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5572,23 +5577,15 @@
       <c r="B159" s="2" t="n"/>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>Residential unit summary[]</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
-        <is>
-          <t>Proposed unit breakdown[]</t>
-        </is>
-      </c>
-      <c r="E159" s="2" t="inlineStr">
-        <is>
-          <t>Total units</t>
-        </is>
-      </c>
+          <t>Total existing units</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr"/>
+      <c r="E159" s="2" t="inlineStr"/>
       <c r="F159" s="2" t="inlineStr"/>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>Total number of units</t>
+          <t>The total number of existing units</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -5598,7 +5595,7 @@
       </c>
       <c r="I159" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5607,7 +5604,7 @@
       <c r="B160" s="2" t="n"/>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Total existing units</t>
+          <t>Total proposed units</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr"/>
@@ -5615,7 +5612,7 @@
       <c r="F160" s="2" t="inlineStr"/>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>The total number of existing units</t>
+          <t>The total number of proposed units</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
@@ -5634,7 +5631,7 @@
       <c r="B161" s="2" t="n"/>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>Total proposed units</t>
+          <t>Net change</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr"/>
@@ -5642,7 +5639,7 @@
       <c r="F161" s="2" t="inlineStr"/>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>The total number of proposed units</t>
+          <t>Calculated net change in units</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
@@ -5657,11 +5654,19 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="2" t="n"/>
-      <c r="B162" s="2" t="n"/>
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>Site area</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>How big the site is including relevant measurements</t>
+        </is>
+      </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>Net change</t>
+          <t>Site area in hectares</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr"/>
@@ -5669,7 +5674,7 @@
       <c r="F162" s="2" t="inlineStr"/>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>Calculated net change in units</t>
+          <t>The size of the site in hectares</t>
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr">
@@ -5684,19 +5689,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="2" t="inlineStr">
-        <is>
-          <t>Site area</t>
-        </is>
-      </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>How big the site is including relevant measurements</t>
-        </is>
-      </c>
+      <c r="A163" s="2" t="n"/>
+      <c r="B163" s="2" t="n"/>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>Site area in hectares</t>
+          <t>Site area provided by</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr"/>
@@ -5704,39 +5701,51 @@
       <c r="F163" s="2" t="inlineStr"/>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>The size of the site in hectares</t>
+          <t>Who provided the site area value</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I163" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="2" t="n"/>
-      <c r="B164" s="2" t="n"/>
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>Site details</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>Where the proposed development will be built.</t>
+        </is>
+      </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>Site area provided by</t>
-        </is>
-      </c>
-      <c r="D164" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>Site boundary</t>
+        </is>
+      </c>
       <c r="E164" s="2" t="inlineStr"/>
       <c r="F164" s="2" t="inlineStr"/>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>Who provided the site area value</t>
+          <t>Geometry of the site of the development, typically in GeoJSON format</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>wkt</t>
         </is>
       </c>
       <c r="I164" s="2" t="inlineStr">
@@ -5746,16 +5755,8 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="inlineStr">
-        <is>
-          <t>Site details</t>
-        </is>
-      </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>Where the proposed development will be built.</t>
-        </is>
-      </c>
+      <c r="A165" s="2" t="n"/>
+      <c r="B165" s="2" t="n"/>
       <c r="C165" s="2" t="inlineStr">
         <is>
           <t>Site locations[]</t>
@@ -5763,19 +5764,19 @@
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>Site boundary</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr"/>
       <c r="F165" s="2" t="inlineStr"/>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>Geometry of the site of the development, typically in GeoJSON format</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
-          <t>wkt</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I165" s="2" t="inlineStr">
@@ -5794,14 +5795,14 @@
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr"/>
       <c r="F166" s="2" t="inlineStr"/>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
@@ -5825,19 +5826,19 @@
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Easting</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr"/>
       <c r="F167" s="2" t="inlineStr"/>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I167" s="2" t="inlineStr">
@@ -5856,14 +5857,14 @@
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>Easting</t>
+          <t>Northing</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr"/>
       <c r="F168" s="2" t="inlineStr"/>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
+          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
@@ -5887,14 +5888,14 @@
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>Northing</t>
+          <t>Latitude</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr"/>
       <c r="F169" s="2" t="inlineStr"/>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
+          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
@@ -5918,14 +5919,14 @@
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>Latitude</t>
+          <t>Longitude</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr"/>
       <c r="F170" s="2" t="inlineStr"/>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
@@ -5949,19 +5950,19 @@
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>Longitude</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr"/>
       <c r="F171" s="2" t="inlineStr"/>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>A text description providing details about the subject. For parking changes, this describes how the proposed works affect existing car parking arrangements.</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I171" s="2" t="inlineStr">
@@ -5980,14 +5981,14 @@
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>UPRNs[]</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr"/>
       <c r="F172" s="2" t="inlineStr"/>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>A text description providing details about the subject. For parking changes, this describes how the proposed works affect existing car parking arrangements.</t>
+          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
@@ -6002,50 +6003,46 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="2" t="n"/>
-      <c r="B173" s="2" t="n"/>
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>Site Visit Details</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>Information to help the planning authority arrange a site visit</t>
+        </is>
+      </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="D173" s="2" t="inlineStr">
-        <is>
-          <t>UPRNs[]</t>
-        </is>
-      </c>
+          <t>Site seen from public area</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr"/>
       <c r="E173" s="2" t="inlineStr"/>
       <c r="F173" s="2" t="inlineStr"/>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
+          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="2" t="inlineStr">
-        <is>
-          <t>Site Visit Details</t>
-        </is>
-      </c>
-      <c r="B174" s="2" t="inlineStr">
-        <is>
-          <t>Information to help the planning authority arrange a site visit</t>
-        </is>
-      </c>
+      <c r="A174" s="2" t="n"/>
+      <c r="B174" s="2" t="n"/>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>Site seen from public area</t>
+          <t>Site visit contact type</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr"/>
@@ -6053,12 +6050,12 @@
       <c r="F174" s="2" t="inlineStr"/>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
+          <t>Indicates who the authority should contact to arrange a site visit</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I174" s="2" t="inlineStr">
@@ -6072,7 +6069,7 @@
       <c r="B175" s="2" t="n"/>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>Site visit contact type</t>
+          <t>Contact reference</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr"/>
@@ -6080,17 +6077,17 @@
       <c r="F175" s="2" t="inlineStr"/>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>Indicates who the authority should contact to arrange a site visit</t>
+          <t>The reference of the applicant or agent who should be contacted for site visits</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I175" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -6099,15 +6096,19 @@
       <c r="B176" s="2" t="n"/>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>Contact reference</t>
-        </is>
-      </c>
-      <c r="D176" s="2" t="inlineStr"/>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>Full name</t>
+        </is>
+      </c>
       <c r="E176" s="2" t="inlineStr"/>
       <c r="F176" s="2" t="inlineStr"/>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+          <t>The complete name of a person</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
@@ -6117,7 +6118,7 @@
       </c>
       <c r="I176" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -6131,14 +6132,14 @@
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>Full name</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr"/>
       <c r="F177" s="2" t="inlineStr"/>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>The complete name of a person</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
@@ -6162,14 +6163,14 @@
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr"/>
       <c r="F178" s="2" t="inlineStr"/>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr">
@@ -6178,37 +6179,6 @@
         </is>
       </c>
       <c r="I178" s="2" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="2" t="n"/>
-      <c r="B179" s="2" t="n"/>
-      <c r="C179" s="2" t="inlineStr">
-        <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="D179" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="E179" s="2" t="inlineStr"/>
-      <c r="F179" s="2" t="inlineStr"/>
-      <c r="G179" s="2" t="inlineStr">
-        <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
-        </is>
-      </c>
-      <c r="H179" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="I179" s="2" t="inlineStr">
         <is>
           <t>MUST</t>
         </is>
@@ -6218,46 +6188,46 @@
   <mergeCells count="44">
     <mergeCell ref="B35:B40"/>
     <mergeCell ref="A68:A77"/>
-    <mergeCell ref="B141:B146"/>
     <mergeCell ref="B31:B34"/>
-    <mergeCell ref="B147:B162"/>
+    <mergeCell ref="B146:B161"/>
     <mergeCell ref="B109:B123"/>
     <mergeCell ref="B55"/>
-    <mergeCell ref="B129:B140"/>
-    <mergeCell ref="A147:A162"/>
+    <mergeCell ref="A164:A172"/>
     <mergeCell ref="B124:B128"/>
     <mergeCell ref="B84:B90"/>
+    <mergeCell ref="B140:B145"/>
+    <mergeCell ref="A162:A163"/>
     <mergeCell ref="B2:B18"/>
     <mergeCell ref="A59:A61"/>
     <mergeCell ref="B62:B67"/>
     <mergeCell ref="A78:A83"/>
     <mergeCell ref="A91:A108"/>
-    <mergeCell ref="A174:A179"/>
+    <mergeCell ref="A129:A139"/>
     <mergeCell ref="B56:B58"/>
     <mergeCell ref="B41:B54"/>
     <mergeCell ref="B19:B22"/>
     <mergeCell ref="B59:B61"/>
+    <mergeCell ref="B162:B163"/>
     <mergeCell ref="B23:B30"/>
-    <mergeCell ref="A163:A164"/>
+    <mergeCell ref="A173:A178"/>
+    <mergeCell ref="B164:B172"/>
     <mergeCell ref="B78:B83"/>
-    <mergeCell ref="A165:A173"/>
     <mergeCell ref="B91:B108"/>
     <mergeCell ref="A2:A18"/>
-    <mergeCell ref="B174:B179"/>
+    <mergeCell ref="B129:B139"/>
     <mergeCell ref="A109:A123"/>
     <mergeCell ref="A19:A22"/>
-    <mergeCell ref="A141:A146"/>
+    <mergeCell ref="A146:A161"/>
     <mergeCell ref="A35:A40"/>
     <mergeCell ref="A124:A128"/>
-    <mergeCell ref="B163:B164"/>
     <mergeCell ref="A84:A90"/>
     <mergeCell ref="A31:A34"/>
+    <mergeCell ref="A140:A145"/>
     <mergeCell ref="A55"/>
     <mergeCell ref="A41:A54"/>
-    <mergeCell ref="B165:B173"/>
     <mergeCell ref="B68:B77"/>
     <mergeCell ref="A23:A30"/>
-    <mergeCell ref="A129:A140"/>
+    <mergeCell ref="B173:B178"/>
     <mergeCell ref="A56:A58"/>
     <mergeCell ref="A62:A67"/>
   </mergeCells>

--- a/generated/spreadsheet/outline-planning-outline.xlsx
+++ b/generated/spreadsheet/outline-planning-outline.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I178"/>
+  <dimension ref="A1:I177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -437,7 +437,7 @@
     <col width="29" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="72" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -491,29 +491,29 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Submission reference</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>A unique reference for the submission</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -532,7 +532,7 @@
       <c r="B3" s="2" t="n"/>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -563,19 +563,19 @@
       <c r="B4" s="2" t="n"/>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Planning authority</t>
+          <t>Specification profile</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
+          <t>The specification profile used to determine context-specific allowed codelist values for the application</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -594,24 +594,24 @@
       <c r="B5" s="2" t="n"/>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Submission date</t>
+          <t>Planning authority</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Date the application is submitted in YYYY-MM-DD format</t>
+          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -625,24 +625,24 @@
       <c r="B6" s="2" t="n"/>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Modules[]</t>
+          <t>Submitted at</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>List of required modules for this application that can be used to validate the application</t>
+          <t>The date and time the application was submitted</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -656,28 +656,24 @@
       <c r="B7" s="2" t="n"/>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Documents[]</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Created at</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
+          <t>The date and time the submission payload was created</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -691,7 +687,7 @@
       <c r="B8" s="2" t="n"/>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -701,13 +697,13 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>The name or title of the document</t>
+          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -726,7 +722,7 @@
       <c r="B9" s="2" t="n"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -736,13 +732,13 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Brief description of what the document contains</t>
+          <t>The name or title of the document</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -752,7 +748,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -761,7 +757,7 @@
       <c r="B10" s="2" t="n"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -771,23 +767,23 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Document types[]</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>List of codelist references that the document covers</t>
+          <t>Brief description of what the document contains</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -796,7 +792,7 @@
       <c r="B11" s="2" t="n"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -806,18 +802,18 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Uploaded date</t>
+          <t>Document types[]</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>The date the document was uploaded to the application</t>
+          <t>List of codelist references that the document covers</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -831,7 +827,7 @@
       <c r="B12" s="2" t="n"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -841,27 +837,23 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Base64</t>
-        </is>
-      </c>
+          <t>Uploaded date</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Base64-encoded content of the file for inline file uploads</t>
+          <t>The date the document was uploaded to the application</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -870,7 +862,7 @@
       <c r="B13" s="2" t="n"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -885,12 +877,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Filename</t>
+          <t>Base64</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Name of the file being uploaded</t>
+          <t>Base64-encoded content of the file for inline file uploads</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -900,7 +892,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -909,7 +901,7 @@
       <c r="B14" s="2" t="n"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -924,12 +916,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>MIME type</t>
+          <t>Filename</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>The file's MIME type such as application/pdf or image/jpeg</t>
+          <t>Name of the file being uploaded</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -939,7 +931,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -948,7 +940,7 @@
       <c r="B15" s="2" t="n"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -963,17 +955,17 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>File size</t>
+          <t>MIME type</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Size of the file in bytes that can be used to enforce limits</t>
+          <t>The file's MIME type such as application/pdf or image/jpeg</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -987,33 +979,37 @@
       <c r="B16" s="2" t="n"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Fee</t>
+          <t>Documents[]</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Amount</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr"/>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>File size</t>
+        </is>
+      </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>The total amount due for the application fee</t>
+          <t>Size of the file in bytes that can be used to enforce limits</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1018,7 @@
       <c r="B17" s="2" t="n"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1032,18 +1028,18 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Amount paid</t>
+          <t>Amount</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>The amount paid towards the application fee</t>
+          <t>The total amount due for the application fee</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1057,7 +1053,7 @@
       <c r="B18" s="2" t="n"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1067,48 +1063,48 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Transactions[]</t>
+          <t>Amount paid</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>References to payments or financial transactions related to this application</t>
+          <t>The amount paid towards the application fee</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Agent contact details</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Name and contact information if an agent is being used.</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="n"/>
+      <c r="B19" s="2" t="n"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Agent reference</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr"/>
-      <c r="E19" s="2" t="inlineStr"/>
+          <t>Submission details</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Fee</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Transactions[]</t>
+        </is>
+      </c>
       <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>A reference to an agent object</t>
+          <t>References to payments or financial transactions related to this application</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1118,28 +1114,32 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n"/>
-      <c r="B20" s="2" t="n"/>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Agent contact details</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information if an agent is being used.</t>
+        </is>
+      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Agent reference</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr"/>
       <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>A reference to an agent object</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1163,18 +1163,14 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr"/>
       <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1184,7 +1180,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1203,18 +1199,18 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Contact priority</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1224,47 +1220,51 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Agent details</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>Name and contact information if an agent is being used.</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="n"/>
+      <c r="B23" s="2" t="n"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>agent</t>
+          <t>Contact details</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Contact priority</t>
+        </is>
+      </c>
       <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n"/>
-      <c r="B24" s="2" t="n"/>
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Agent details</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information if an agent is being used.</t>
+        </is>
+      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>agent</t>
@@ -1272,18 +1272,14 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1293,7 +1289,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1312,13 +1308,13 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1328,7 +1324,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1347,13 +1343,13 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr"/>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1382,13 +1378,13 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr"/>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1417,13 +1413,13 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1433,7 +1429,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1447,14 +1443,18 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="F29" s="2" t="inlineStr"/>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>The name of a company (that the agent works for)</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1478,19 +1478,19 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>User role</t>
+          <t>Company</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="2" t="inlineStr"/>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>The role of the named individual. Agent or proxy</t>
+          <t>The name of a company (that the agent works for)</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -1500,58 +1500,58 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>Applicant contact details</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>Telephone number and email address of the applicant.</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="n"/>
+      <c r="B31" s="2" t="n"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Applicant reference</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr"/>
+          <t>agent</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>User role</t>
+        </is>
+      </c>
       <c r="E31" s="2" t="inlineStr"/>
       <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Reference to match contact details to a named individual from the applicant details component</t>
+          <t>The role of the named individual. Agent or proxy</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n"/>
-      <c r="B32" s="2" t="n"/>
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Applicant contact details</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Telephone number and email address of the applicant.</t>
+        </is>
+      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Applicant reference</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr"/>
       <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>Reference to match contact details to a named individual from the applicant details component</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -1575,18 +1575,14 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr"/>
       <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -1596,7 +1592,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1615,18 +1611,18 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Contact priority</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -1636,47 +1632,51 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>Applicant details</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>Name and contact information for the parties making the application.</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="n"/>
+      <c r="B35" s="2" t="n"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Applicants[]</t>
+          <t>Contact details</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Contact priority</t>
+        </is>
+      </c>
       <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n"/>
-      <c r="B36" s="2" t="n"/>
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Applicant details</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information for the parties making the application.</t>
+        </is>
+      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>Applicants[]</t>
@@ -1684,18 +1684,14 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -1705,7 +1701,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1724,13 +1720,13 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -1740,7 +1736,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1759,13 +1755,13 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr"/>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -1794,13 +1790,13 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr"/>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -1829,13 +1825,13 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -1845,68 +1841,72 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>Biodiversity net gain</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>How any natural habitats on the development site will be improved by the proposed works.</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="n"/>
+      <c r="B41" s="2" t="n"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity gain condition applies</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr"/>
-      <c r="E41" s="2" t="inlineStr"/>
+          <t>Applicants[]</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="F41" s="2" t="inlineStr"/>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Does the applicant believe the Biodiversity Gain Condition applies to this application</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n"/>
-      <c r="B42" s="2" t="n"/>
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Biodiversity net gain</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>How any natural habitats on the development site will be improved by the proposed works.</t>
+        </is>
+      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity gain condition exemption reason[]</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>Exemption type</t>
-        </is>
-      </c>
+          <t>Biodiversity gain condition applies</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr"/>
       <c r="E42" s="2" t="inlineStr"/>
       <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>The type of biodiversity gain exemption from the bng-exemption-type enum</t>
+          <t>Does the applicant believe the Biodiversity Gain Condition applies to this application</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -1925,19 +1925,19 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Reason</t>
+          <t>Exemption type</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr"/>
       <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>The reason the exemption applies to this proposal</t>
+          <t>The type of biodiversity gain exemption from the bng-exemption-type enum</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -1951,24 +1951,24 @@
       <c r="B44" s="2" t="n"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity net gain details</t>
+          <t>Biodiversity gain condition exemption reason[]</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Pre development date</t>
+          <t>Reason</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr"/>
       <c r="F44" s="2" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Date of pre-development biodiversity value calculation, must align with application or justified earlier date</t>
+          <t>The reason the exemption applies to this proposal</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -1987,19 +1987,19 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Pre development biodiversity value</t>
+          <t>Pre development date</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
       <c r="F45" s="2" t="inlineStr"/>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Calculated biodiversity value in Habitat Biodiversity Units</t>
+          <t>Date of pre-development biodiversity value calculation, must align with application or justified earlier date</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
@@ -2018,24 +2018,24 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Earlier date reason</t>
+          <t>Pre development biodiversity value</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr"/>
       <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Reason for using a pre-development date that is earlier than the application submission</t>
+          <t>Calculated biodiversity value in Habitat Biodiversity Units</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2049,19 +2049,19 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Habitat loss after 2020</t>
+          <t>Earlier date reason</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr"/>
       <c r="F47" s="2" t="inlineStr"/>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether there has been degradation of onsite habitat(s) after 30 Jan 2020</t>
+          <t>Reason for using a pre-development date that is earlier than the application submission</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -2080,28 +2080,24 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Habitat loss details</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>Loss date</t>
-        </is>
-      </c>
+          <t>Habitat loss after 2020</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr"/>
       <c r="F48" s="2" t="inlineStr"/>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Date the activity causing habitat loss or degradation occurred</t>
+          <t>Indicates whether there has been degradation of onsite habitat(s) after 30 Jan 2020</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2120,18 +2116,18 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Pre loss biodiversity value</t>
+          <t>Loss date</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr"/>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity value immediately before habitat loss or degradation occurred, measured in Habitat Biodiversity Units</t>
+          <t>Date the activity causing habitat loss or degradation occurred</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
@@ -2155,23 +2151,23 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Supporting evidence</t>
+          <t>Pre loss biodiversity value</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr"/>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Description or reference to supporting documents for habitat loss or degradation evidence</t>
+          <t>Biodiversity value immediately before habitat loss or degradation occurred, measured in Habitat Biodiversity Units</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2185,24 +2181,28 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Metric publication date</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr"/>
+          <t>Habitat loss details</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Supporting evidence</t>
+        </is>
+      </c>
       <c r="F51" s="2" t="inlineStr"/>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Publication date of the biodiversity metric tool used for calculations</t>
+          <t>Description or reference to supporting documents for habitat loss or degradation evidence</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2216,19 +2216,19 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Irreplaceable habitats</t>
+          <t>Metric publication date</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr"/>
       <c r="F52" s="2" t="inlineStr"/>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether the site contains any irreplaceable habitats</t>
+          <t>Publication date of the biodiversity metric tool used for calculations</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
@@ -2247,24 +2247,24 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Irreplaceable habitats details</t>
+          <t>Irreplaceable habitats</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr"/>
       <c r="F53" s="2" t="inlineStr"/>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Description and references for any irreplaceable habitats identified on the site</t>
+          <t>Indicates whether the site contains any irreplaceable habitats</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2278,18 +2278,14 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Irreplaceable habitats details</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr"/>
       <c r="F54" s="2" t="inlineStr"/>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Description and references for any irreplaceable habitats identified on the site</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -2299,32 +2295,32 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>Checklist</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
-        </is>
-      </c>
+      <c r="A55" s="2" t="n"/>
+      <c r="B55" s="2" t="n"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>National requirement types[]</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr"/>
-      <c r="E55" s="2" t="inlineStr"/>
+          <t>Biodiversity net gain details</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="F55" s="2" t="inlineStr"/>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>List of the document types required for the given application type</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -2341,17 +2337,17 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Conflict of interest</t>
+          <t>Checklist</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
+          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Conflict to declare</t>
+          <t>National requirement types[]</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr"/>
@@ -2359,12 +2355,12 @@
       <c r="F56" s="2" t="inlineStr"/>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
+          <t>List of the document types required for the given application type</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -2374,11 +2370,19 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n"/>
-      <c r="B57" s="2" t="n"/>
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Conflict of interest</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
+        </is>
+      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Conflict person name</t>
+          <t>Conflict to declare</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr"/>
@@ -2386,17 +2390,17 @@
       <c r="F57" s="2" t="inlineStr"/>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Name of the individual with the conflict of interest that matches one of the names provided in applicants/agent section</t>
+          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2405,7 +2409,7 @@
       <c r="B58" s="2" t="n"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Conflict details</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr"/>
@@ -2413,7 +2417,7 @@
       <c r="F58" s="2" t="inlineStr"/>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
+          <t>Reference to the applicant or agent with the conflict</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -2428,19 +2432,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>Declaration</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>Signed and dated verification of the application's accuracy.</t>
-        </is>
-      </c>
+      <c r="A59" s="2" t="n"/>
+      <c r="B59" s="2" t="n"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Conflict details</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr"/>
@@ -2448,7 +2444,7 @@
       <c r="F59" s="2" t="inlineStr"/>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>A name of a person</t>
+          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -2458,16 +2454,24 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n"/>
-      <c r="B60" s="2" t="n"/>
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Declaration</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Signed and dated verification of the application's accuracy.</t>
+        </is>
+      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr"/>
@@ -2475,12 +2479,12 @@
       <c r="F60" s="2" t="inlineStr"/>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>Declaration must be made by an applicant or agent making the application</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
@@ -2494,7 +2498,7 @@
       <c r="B61" s="2" t="n"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr"/>
@@ -2502,12 +2506,12 @@
       <c r="F61" s="2" t="inlineStr"/>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
@@ -2517,36 +2521,24 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>Employment</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>How the proposed development will impact existing and proposed employee numbers</t>
-        </is>
-      </c>
+      <c r="A62" s="2" t="n"/>
+      <c r="B62" s="2" t="n"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Existing employees</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>Full-time</t>
-        </is>
-      </c>
+          <t>Declaration date</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr"/>
       <c r="E62" s="2" t="inlineStr"/>
       <c r="F62" s="2" t="inlineStr"/>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Number of full-time employees</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
@@ -2556,8 +2548,16 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n"/>
-      <c r="B63" s="2" t="n"/>
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Employment</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>How the proposed development will impact existing and proposed employee numbers</t>
+        </is>
+      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>Existing employees</t>
@@ -2565,19 +2565,19 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Part-time</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr"/>
       <c r="F63" s="2" t="inlineStr"/>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Number of part-time employees</t>
+          <t>Number of full-time employees</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
@@ -2596,19 +2596,19 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Total FTE</t>
+          <t>Part-time</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr"/>
       <c r="F64" s="2" t="inlineStr"/>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Total full-time equivalent (FTE)</t>
+          <t>Number of part-time employees</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
@@ -2622,24 +2622,24 @@
       <c r="B65" s="2" t="n"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Proposed employees</t>
+          <t>Existing employees</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Total FTE</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr"/>
       <c r="F65" s="2" t="inlineStr"/>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Number of full-time employees</t>
+          <t>Total full-time equivalent (FTE)</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
@@ -2658,19 +2658,19 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Part-time</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr"/>
       <c r="F66" s="2" t="inlineStr"/>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Number of part-time employees</t>
+          <t>Number of full-time employees</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
@@ -2689,19 +2689,19 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Total FTE</t>
+          <t>Part-time</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr"/>
       <c r="F67" s="2" t="inlineStr"/>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Total full-time equivalent (FTE)</t>
+          <t>Number of part-time employees</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
@@ -2711,36 +2711,28 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>Existing use</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>How the site is currently being used.</t>
-        </is>
-      </c>
+      <c r="A68" s="2" t="n"/>
+      <c r="B68" s="2" t="n"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Existing use details[]</t>
+          <t>Proposed employees</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Use</t>
+          <t>Total FTE</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr"/>
       <c r="F68" s="2" t="inlineStr"/>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>A use class or type of use</t>
+          <t>Total full-time equivalent (FTE)</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
@@ -2750,8 +2742,16 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n"/>
-      <c r="B69" s="2" t="n"/>
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Existing use</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>How the site is currently being used.</t>
+        </is>
+      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>Existing use details[]</t>
@@ -2759,24 +2759,24 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Use details</t>
+          <t>Use</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr"/>
       <c r="F69" s="2" t="inlineStr"/>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Further detail of the use</t>
+          <t>A use class or type of use</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2790,14 +2790,14 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Land part</t>
+          <t>Use details</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr"/>
       <c r="F70" s="2" t="inlineStr"/>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Which part of the land the use relates to</t>
+          <t>Further detail of the use</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2816,20 +2816,24 @@
       <c r="B71" s="2" t="n"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Site vacant</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr"/>
+          <t>Existing use details[]</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Land part</t>
+        </is>
+      </c>
       <c r="E71" s="2" t="inlineStr"/>
       <c r="F71" s="2" t="inlineStr"/>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Is the site currently vacant</t>
+          <t>Which part of the land the use relates to</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
@@ -2843,7 +2847,7 @@
       <c r="B72" s="2" t="n"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Last use details</t>
+          <t>Site vacant</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr"/>
@@ -2851,17 +2855,17 @@
       <c r="F72" s="2" t="inlineStr"/>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Description of the last use of the site</t>
+          <t>Is the site currently vacant</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2870,7 +2874,7 @@
       <c r="B73" s="2" t="n"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Last use end date</t>
+          <t>Last use details</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr"/>
@@ -2878,12 +2882,12 @@
       <c r="F73" s="2" t="inlineStr"/>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Date the last use ended (YYYY-MM-DD format)</t>
+          <t>Description of the last use of the site</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
@@ -2897,7 +2901,7 @@
       <c r="B74" s="2" t="n"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Is contaminated land</t>
+          <t>Last use end date</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr"/>
@@ -2905,17 +2909,17 @@
       <c r="F74" s="2" t="inlineStr"/>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Is the site known to be contaminated?</t>
+          <t>Date the last use ended (YYYY-MM-DD format)</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2924,7 +2928,7 @@
       <c r="B75" s="2" t="n"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Is suspected contaminated land</t>
+          <t>Is contaminated land</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr"/>
@@ -2932,7 +2936,7 @@
       <c r="F75" s="2" t="inlineStr"/>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Is the site suspected of contamination?</t>
+          <t>Is the site known to be contaminated?</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -2951,7 +2955,7 @@
       <c r="B76" s="2" t="n"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Proposed use contamination risk</t>
+          <t>Is suspected contaminated land</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr"/>
@@ -2959,7 +2963,7 @@
       <c r="F76" s="2" t="inlineStr"/>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Is the proposed use vulnerable to the presence of contamination?</t>
+          <t>Is the site suspected of contamination?</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -2978,7 +2982,7 @@
       <c r="B77" s="2" t="n"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Contamination assessment</t>
+          <t>Proposed use contamination risk</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr"/>
@@ -2986,34 +2990,26 @@
       <c r="F77" s="2" t="inlineStr"/>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>Reference to contamination assessment document</t>
+          <t>Is the proposed use vulnerable to the presence of contamination?</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>Flood risk assessment</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>Results of any flood risk assessments made for the development site</t>
-        </is>
-      </c>
+      <c r="A78" s="2" t="n"/>
+      <c r="B78" s="2" t="n"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Flood risk area</t>
+          <t>Contamination assessment</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr"/>
@@ -3021,26 +3017,34 @@
       <c r="F78" s="2" t="inlineStr"/>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Is the site within an area at risk of flooding?</t>
+          <t>Reference to contamination assessment document</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n"/>
-      <c r="B79" s="2" t="n"/>
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Flood risk assessment</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Results of any flood risk assessments made for the development site</t>
+        </is>
+      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Data provided by</t>
+          <t>Flood risk area</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr"/>
@@ -3048,17 +3052,17 @@
       <c r="F79" s="2" t="inlineStr"/>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Who provided the data: Applicant or System/Service?</t>
+          <t>Is the site within an area at risk of flooding?</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3067,7 +3071,7 @@
       <c r="B80" s="2" t="n"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Flood risk assessment</t>
+          <t>Data provided by</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr"/>
@@ -3075,12 +3079,12 @@
       <c r="F80" s="2" t="inlineStr"/>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Reference of the flood risk assessment document</t>
+          <t>Who provided the data: Applicant or System/Service?</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
@@ -3094,7 +3098,7 @@
       <c r="B81" s="2" t="n"/>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Within 20m watercourse</t>
+          <t>Flood risk assessment</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr"/>
@@ -3102,17 +3106,17 @@
       <c r="F81" s="2" t="inlineStr"/>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Whether the development is within 20 metres of a watercourse</t>
+          <t>Reference of the flood risk assessment document</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3121,7 +3125,7 @@
       <c r="B82" s="2" t="n"/>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Increases flood risk</t>
+          <t>Within 20m watercourse</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr"/>
@@ -3129,7 +3133,7 @@
       <c r="F82" s="2" t="inlineStr"/>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Whether the development increases flood risk</t>
+          <t>Whether the development is within 20 metres of a watercourse</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -3148,7 +3152,7 @@
       <c r="B83" s="2" t="n"/>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Surface water disposal[]</t>
+          <t>Increases flood risk</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr"/>
@@ -3156,12 +3160,12 @@
       <c r="F83" s="2" t="inlineStr"/>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Method for disposing of surface water</t>
+          <t>Whether the development increases flood risk</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
@@ -3171,31 +3175,19 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>Hours of operation</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>Proposed operating hours if the proposed development is intended for non-residential use.</t>
-        </is>
-      </c>
+      <c r="A84" s="2" t="n"/>
+      <c r="B84" s="2" t="n"/>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Hours of operation[]</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>Use</t>
-        </is>
-      </c>
+          <t>Surface water disposal[]</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr"/>
       <c r="E84" s="2" t="inlineStr"/>
       <c r="F84" s="2" t="inlineStr"/>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>A use class or type of use</t>
+          <t>Method for disposing of surface water</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -3210,8 +3202,16 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n"/>
-      <c r="B85" s="2" t="n"/>
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>Hours of operation</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Proposed operating hours if the proposed development is intended for non-residential use.</t>
+        </is>
+      </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
           <t>Hours of operation[]</t>
@@ -3219,24 +3219,24 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Use other</t>
+          <t>Use</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr"/>
       <c r="F85" s="2" t="inlineStr"/>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Specify use if use is "other"</t>
+          <t>A use class or type of use</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3250,28 +3250,24 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Operational times[]</t>
-        </is>
-      </c>
-      <c r="E86" s="2" t="inlineStr">
-        <is>
-          <t>Schedule days[]</t>
-        </is>
-      </c>
+          <t>Use other</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr"/>
       <c r="F86" s="2" t="inlineStr"/>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>List of days or day categories that a schedule entry applies to</t>
+          <t>Specify use if use is "other"</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3290,23 +3286,23 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Schedule days[]</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr"/>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>True or False - explicitly state when closed</t>
+          <t>List of days or day categories that a schedule entry applies to</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3325,27 +3321,23 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Time ranges[]</t>
-        </is>
-      </c>
-      <c r="F88" s="2" t="inlineStr">
-        <is>
-          <t>Open time</t>
-        </is>
-      </c>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr"/>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Opening time</t>
+          <t>True or False - explicitly state when closed</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3369,12 +3361,12 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>Close time</t>
+          <t>Open time</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Closing time</t>
+          <t>Opening time</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -3398,80 +3390,88 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
+          <t>Operational times[]</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>Time ranges[]</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>Close time</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>Closing time</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n"/>
+      <c r="B91" s="2" t="n"/>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Hours of operation[]</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
           <t>Hours not known</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr"/>
-      <c r="F90" s="2" t="inlineStr"/>
-      <c r="G90" s="2" t="inlineStr">
-        <is>
-          <t>Applicant states they do not know the hours of operation</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>boolean</t>
-        </is>
-      </c>
-      <c r="I90" s="2" t="inlineStr">
-        <is>
-          <t>MAY</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>Non residential floorspace</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>Details of changes to non-residential floorspace in the proposed development.</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>Non residential change</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr"/>
       <c r="E91" s="2" t="inlineStr"/>
       <c r="F91" s="2" t="inlineStr"/>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Does the proposal involve the loss, gain, or change of non-residential floorspace?</t>
+          <t>Applicant states they do not know the hours of operation</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n"/>
-      <c r="B92" s="2" t="n"/>
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>Non residential floorspace</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Details of changes to non-residential floorspace in the proposed development.</t>
+        </is>
+      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Floorspace details[]</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
-        <is>
-          <t>Use</t>
-        </is>
-      </c>
+          <t>Non residential change</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr"/>
       <c r="E92" s="2" t="inlineStr"/>
       <c r="F92" s="2" t="inlineStr"/>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>A use class or type of use</t>
+          <t>Does the proposal involve the loss, gain, or change of non-residential floorspace?</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -3495,24 +3495,24 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Specified use</t>
+          <t>Use</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr"/>
       <c r="F93" s="2" t="inlineStr"/>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>A specified use if no applicable use class is available</t>
+          <t>A use class or type of use</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3526,19 +3526,19 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Specified use</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr"/>
       <c r="F94" s="2" t="inlineStr"/>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Whether the facility is not applicable</t>
+          <t>A specified use if no applicable use class is available</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
@@ -3693,7 +3693,7 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
@@ -3805,14 +3805,14 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Is existing rooms lost known</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr"/>
       <c r="F103" s="2" t="inlineStr"/>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>Used to explicitly state the use class does not apply to the proposal</t>
+          <t>Whether the total existing rooms that will be lost is known</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
@@ -3836,19 +3836,19 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Is existing rooms lost known</t>
+          <t>Existing rooms lost</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr"/>
       <c r="F104" s="2" t="inlineStr"/>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>Whether the total existing rooms that will be lost is known</t>
+          <t>Existing rooms to be lost by change of use</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
@@ -3867,19 +3867,19 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Existing rooms lost</t>
+          <t>Is total rooms proposed known</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr"/>
       <c r="F105" s="2" t="inlineStr"/>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>Existing rooms to be lost by change of use</t>
+          <t>Whether the total rooms proposed is known</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
@@ -3898,19 +3898,19 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Is total rooms proposed known</t>
+          <t>Total rooms proposed</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr"/>
       <c r="F106" s="2" t="inlineStr"/>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Whether the total rooms proposed is known</t>
+          <t>Total rooms proposed (including change of use)</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
@@ -3929,50 +3929,54 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Total rooms proposed</t>
+          <t>Net additional rooms</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr"/>
       <c r="F107" s="2" t="inlineStr"/>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Total rooms proposed (including change of use)</t>
+          <t>Net additional rooms following development</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="n"/>
-      <c r="B108" s="2" t="n"/>
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>Ownership certificates and agricultural land declaration</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
+        </is>
+      </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Room details[]</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
-        <is>
-          <t>Net additional rooms</t>
-        </is>
-      </c>
+          <t>Sole owner</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr"/>
       <c r="E108" s="2" t="inlineStr"/>
       <c r="F108" s="2" t="inlineStr"/>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Net additional rooms following development</t>
+          <t>Is the applicant the sole owner of the land?</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
@@ -3982,19 +3986,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="inlineStr">
-        <is>
-          <t>Ownership certificates and agricultural land declaration</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
-        </is>
-      </c>
+      <c r="A109" s="2" t="n"/>
+      <c r="B109" s="2" t="n"/>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Sole owner</t>
+          <t>Agricultural tenants</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr"/>
@@ -4002,7 +3998,7 @@
       <c r="F109" s="2" t="inlineStr"/>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>Is the applicant the sole owner of the land?</t>
+          <t>Are there any agricultural tenants on the land?</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -4021,25 +4017,33 @@
       <c r="B110" s="2" t="n"/>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Agricultural tenants</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr"/>
-      <c r="E110" s="2" t="inlineStr"/>
+          <t>Owners and tenants[]</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
       <c r="F110" s="2" t="inlineStr"/>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>Are there any agricultural tenants on the land?</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4058,13 +4062,13 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr"/>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -4074,7 +4078,7 @@
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4093,13 +4097,13 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr"/>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -4128,13 +4132,13 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr"/>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -4163,13 +4167,13 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr"/>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -4179,7 +4183,7 @@
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4193,23 +4197,19 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E115" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Notice served date</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr"/>
       <c r="F115" s="2" t="inlineStr"/>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Date when notice was served</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr">
@@ -4223,24 +4223,20 @@
       <c r="B116" s="2" t="n"/>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Owners and tenants[]</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
-        <is>
-          <t>Notice date</t>
-        </is>
-      </c>
+          <t>Ownership certificate type</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr"/>
       <c r="E116" s="2" t="inlineStr"/>
       <c r="F116" s="2" t="inlineStr"/>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>Date when notice was served</t>
+          <t>The type of ownership certificate based on ownership and tenancy status</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
@@ -4343,7 +4339,7 @@
       <c r="B120" s="2" t="n"/>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Ownership certificate type</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr"/>
@@ -4351,17 +4347,17 @@
       <c r="F120" s="2" t="inlineStr"/>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>The type of ownership certificate based on ownership and tenancy status</t>
+          <t>Declaration must be made by an applicant or agent making the application</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4370,7 +4366,7 @@
       <c r="B121" s="2" t="n"/>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Applicant signature</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr"/>
@@ -4378,17 +4374,17 @@
       <c r="F121" s="2" t="inlineStr"/>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>Digital signature of the applicant</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4397,7 +4393,7 @@
       <c r="B122" s="2" t="n"/>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Agent signature</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr"/>
@@ -4405,26 +4401,34 @@
       <c r="F122" s="2" t="inlineStr"/>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>Digital signature of the agent (if applicable)</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="n"/>
-      <c r="B123" s="2" t="n"/>
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>Pre-application advice</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>Details of pre-application advice previously received from the planning authority</t>
+        </is>
+      </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Pre-application advice sought</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr"/>
@@ -4432,34 +4436,26 @@
       <c r="F123" s="2" t="inlineStr"/>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Whether pre-application advice has been sought from the planning authority</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="inlineStr">
-        <is>
-          <t>Pre-application advice</t>
-        </is>
-      </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
-        </is>
-      </c>
+      <c r="A124" s="2" t="n"/>
+      <c r="B124" s="2" t="n"/>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Pre-application advice sought</t>
+          <t>Officer name</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr"/>
@@ -4467,17 +4463,17 @@
       <c r="F124" s="2" t="inlineStr"/>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>Whether pre-application advice has been sought from the planning authority</t>
+          <t>Name of the planning officer who provided the pre-application advice</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4486,7 +4482,7 @@
       <c r="B125" s="2" t="n"/>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Officer name</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr"/>
@@ -4494,7 +4490,7 @@
       <c r="F125" s="2" t="inlineStr"/>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Name of the planning officer who provided the pre-application advice</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -4513,7 +4509,7 @@
       <c r="B126" s="2" t="n"/>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Advice date</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr"/>
@@ -4521,12 +4517,12 @@
       <c r="F126" s="2" t="inlineStr"/>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr">
@@ -4540,7 +4536,7 @@
       <c r="B127" s="2" t="n"/>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>Advice date</t>
+          <t>Advice summary</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr"/>
@@ -4548,12 +4544,12 @@
       <c r="F127" s="2" t="inlineStr"/>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
+          <t>Summary of the pre-application advice received from the planning authority</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I127" s="2" t="inlineStr">
@@ -4563,11 +4559,20 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="n"/>
-      <c r="B128" s="2" t="n"/>
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>Processes machinery waste</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">How waste will be managed on the site
+</t>
+        </is>
+      </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Advice summary</t>
+          <t>Site activity details</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr"/>
@@ -4575,7 +4580,7 @@
       <c r="F128" s="2" t="inlineStr"/>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>Summary of the pre-application advice received from the planning authority</t>
+          <t>Description of activities, processes, and end products including site operations, plant, ventilation, and machinery</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
@@ -4585,25 +4590,16 @@
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="inlineStr">
-        <is>
-          <t>Processes machinery waste</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">How waste will be managed on the site
-</t>
-        </is>
-      </c>
+      <c r="A129" s="2" t="n"/>
+      <c r="B129" s="2" t="n"/>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Site activity details</t>
+          <t>Proposal waste management</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr"/>
@@ -4611,12 +4607,12 @@
       <c r="F129" s="2" t="inlineStr"/>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>Description of activities, processes, and end products including site operations, plant, ventilation, and machinery</t>
+          <t>Whether the proposal involves any waste management facility that is relevant to the proposal</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr">
@@ -4630,20 +4626,24 @@
       <c r="B130" s="2" t="n"/>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Proposal waste management</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr"/>
+          <t>Waste management[]</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Waste management facility type</t>
+        </is>
+      </c>
       <c r="E130" s="2" t="inlineStr"/>
       <c r="F130" s="2" t="inlineStr"/>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>Whether the proposal involves any waste management facility that is relevant to the proposal</t>
+          <t>Type of waste management facility being described in this entry</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
@@ -4662,19 +4662,19 @@
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>Waste management facility type</t>
+          <t>Total capacity</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr"/>
       <c r="F131" s="2" t="inlineStr"/>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>Type of waste management facility being described in this entry</t>
+          <t>Total capacity of void in cubic metres (or tonnes/litres)</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I131" s="2" t="inlineStr">
@@ -4693,19 +4693,19 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Total capacity</t>
+          <t>Unit type</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr"/>
       <c r="F132" s="2" t="inlineStr"/>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>Total capacity of void in cubic metres (or tonnes/litres)</t>
+          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr">
@@ -4724,19 +4724,19 @@
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>Unit type</t>
+          <t>Annual throughput</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr"/>
       <c r="F133" s="2" t="inlineStr"/>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
+          <t>Maximum annual operational throughput in tonnes/litres</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I133" s="2" t="inlineStr">
@@ -4755,19 +4755,19 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Annual throughput</t>
+          <t>Unit type</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr"/>
       <c r="F134" s="2" t="inlineStr"/>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>Maximum annual operational throughput in tonnes/litres</t>
+          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr">
@@ -4781,29 +4781,29 @@
       <c r="B135" s="2" t="n"/>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>Waste management[]</t>
+          <t>Waste streams throughput</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>Unit type</t>
+          <t>Municipal</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr"/>
       <c r="F135" s="2" t="inlineStr"/>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
+          <t>Maximum throughput for municipal waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4817,19 +4817,19 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>Municipal</t>
+          <t>Construction demolition</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr"/>
       <c r="F136" s="2" t="inlineStr"/>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for municipal waste (annual throughput in tonnes/litres)</t>
+          <t>Maximum throughput for construction and demolition waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr">
@@ -4848,19 +4848,19 @@
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>Construction demolition</t>
+          <t>Commercial industrial</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr"/>
       <c r="F137" s="2" t="inlineStr"/>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for construction and demolition waste (annual throughput in tonnes/litres)</t>
+          <t>Maximum throughput for commercial and industrial waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I137" s="2" t="inlineStr">
@@ -4879,19 +4879,19 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Commercial industrial</t>
+          <t>Hazardous</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr"/>
       <c r="F138" s="2" t="inlineStr"/>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for commercial and industrial waste (annual throughput in tonnes/litres)</t>
+          <t>Maximum throughput for hazardous waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I138" s="2" t="inlineStr">
@@ -4901,50 +4901,46 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="2" t="n"/>
-      <c r="B139" s="2" t="n"/>
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>Description of the proposal</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>What development, works or change of use is proposed</t>
+        </is>
+      </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>Waste streams throughput</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
-        <is>
-          <t>Hazardous</t>
-        </is>
-      </c>
+          <t>Proposal description</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr"/>
       <c r="E139" s="2" t="inlineStr"/>
       <c r="F139" s="2" t="inlineStr"/>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for hazardous waste (annual throughput in tonnes/litres)</t>
+          <t>A description of what is being proposed, including the development, works, or change of use</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="inlineStr">
-        <is>
-          <t>Description of the proposal</t>
-        </is>
-      </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>What development, works or change of use is proposed</t>
-        </is>
-      </c>
+      <c r="A140" s="2" t="n"/>
+      <c r="B140" s="2" t="n"/>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Proposal description</t>
+          <t>Reserved matters[]</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr"/>
@@ -4952,12 +4948,12 @@
       <c r="F140" s="2" t="inlineStr"/>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>A description of what is being proposed, including the development, works, or change of use</t>
+          <t>Identifies which reserved matters are being submitted for approval as part of this application</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr">
@@ -4971,7 +4967,7 @@
       <c r="B141" s="2" t="n"/>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>Reserved matters[]</t>
+          <t>Proposal started</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr"/>
@@ -4979,12 +4975,12 @@
       <c r="F141" s="2" t="inlineStr"/>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>Identifies which reserved matters are being submitted for approval as part of this application</t>
+          <t>Has any work on the proposal already been started</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I141" s="2" t="inlineStr">
@@ -4998,7 +4994,7 @@
       <c r="B142" s="2" t="n"/>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Proposal started</t>
+          <t>Proposal start date</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr"/>
@@ -5006,17 +5002,17 @@
       <c r="F142" s="2" t="inlineStr"/>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been started</t>
+          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5025,7 +5021,7 @@
       <c r="B143" s="2" t="n"/>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>Proposal start date</t>
+          <t>Proposal completed</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr"/>
@@ -5033,17 +5029,17 @@
       <c r="F143" s="2" t="inlineStr"/>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
+          <t>Has any work on the proposal already been completed</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I143" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5052,7 +5048,7 @@
       <c r="B144" s="2" t="n"/>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Proposal completed</t>
+          <t>Proposal completion date</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr"/>
@@ -5060,26 +5056,34 @@
       <c r="F144" s="2" t="inlineStr"/>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been completed</t>
+          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="2" t="n"/>
-      <c r="B145" s="2" t="n"/>
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>Residential units</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>Details of the residential units that make up both the current and proposed development.</t>
+        </is>
+      </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>Proposal completion date</t>
+          <t>Residential unit change</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr"/>
@@ -5087,47 +5091,43 @@
       <c r="F145" s="2" t="inlineStr"/>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
+          <t>Proposal includes the gain, loss or change of use of residential units</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="inlineStr">
-        <is>
-          <t>Residential units</t>
-        </is>
-      </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>Details of the residential units that make up both the current and proposed development.</t>
-        </is>
-      </c>
+      <c r="A146" s="2" t="n"/>
+      <c r="B146" s="2" t="n"/>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Residential unit change</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr"/>
+          <t>Residential unit summary[]</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>Tenure type</t>
+        </is>
+      </c>
       <c r="E146" s="2" t="inlineStr"/>
       <c r="F146" s="2" t="inlineStr"/>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>Proposal includes the gain, loss or change of use of residential units</t>
+          <t>Category of housing tenure</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr">
@@ -5146,14 +5146,14 @@
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>Tenure type</t>
+          <t>Housing type</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr"/>
       <c r="F147" s="2" t="inlineStr"/>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>Category of housing tenure</t>
+          <t>Type of housing</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
@@ -5177,19 +5177,23 @@
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>Housing type</t>
-        </is>
-      </c>
-      <c r="E148" s="2" t="inlineStr"/>
+          <t>Existing unit breakdown[]</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>Units unknown</t>
+        </is>
+      </c>
       <c r="F148" s="2" t="inlineStr"/>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>Type of housing</t>
+          <t>Whether the number of units is unknown</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I148" s="2" t="inlineStr">
@@ -5213,13 +5217,17 @@
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>Units unknown</t>
-        </is>
-      </c>
-      <c r="F149" s="2" t="inlineStr"/>
+          <t>Units per bedroom number[]</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>No bedrooms unknown</t>
+        </is>
+      </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>Whether the number of units is unknown</t>
+          <t>Set to true when counting units where bedroom number is unknown</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
@@ -5253,22 +5261,22 @@
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>No bedrooms unknown</t>
+          <t>Number of bedrooms</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>Set to true when counting units where bedroom number is unknown</t>
+          <t>The number of bedrooms in unit</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5292,22 +5300,22 @@
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>Number of bedrooms</t>
+          <t>Units</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>The number of bedrooms in unit</t>
+          <t>The number of units of that bedroom count</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5326,27 +5334,23 @@
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>Units per bedroom number[]</t>
-        </is>
-      </c>
-      <c r="F152" s="2" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
+          <t>Total units</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr"/>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>The number of units of that bedroom count</t>
+          <t>Total number of units</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5360,28 +5364,28 @@
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>Existing unit breakdown[]</t>
+          <t>Proposed unit breakdown[]</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>Total units</t>
+          <t>Units unknown</t>
         </is>
       </c>
       <c r="F153" s="2" t="inlineStr"/>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>Total number of units</t>
+          <t>Whether the number of units is unknown</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5400,13 +5404,17 @@
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>Units unknown</t>
-        </is>
-      </c>
-      <c r="F154" s="2" t="inlineStr"/>
+          <t>Units per bedroom number[]</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>No bedrooms unknown</t>
+        </is>
+      </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>Whether the number of units is unknown</t>
+          <t>Set to true when counting units where bedroom number is unknown</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
@@ -5440,22 +5448,22 @@
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>No bedrooms unknown</t>
+          <t>Number of bedrooms</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Set to true when counting units where bedroom number is unknown</t>
+          <t>The number of bedrooms in unit</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I155" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5479,22 +5487,22 @@
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>Number of bedrooms</t>
+          <t>Units</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>The number of bedrooms in unit</t>
+          <t>The number of units of that bedroom count</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5513,27 +5521,23 @@
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>Units per bedroom number[]</t>
-        </is>
-      </c>
-      <c r="F157" s="2" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
+          <t>Total units</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr"/>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>The number of units of that bedroom count</t>
+          <t>Total number of units</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I157" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5542,33 +5546,25 @@
       <c r="B158" s="2" t="n"/>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>Residential unit summary[]</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
-        <is>
-          <t>Proposed unit breakdown[]</t>
-        </is>
-      </c>
-      <c r="E158" s="2" t="inlineStr">
-        <is>
-          <t>Total units</t>
-        </is>
-      </c>
+          <t>Total existing units</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr"/>
+      <c r="E158" s="2" t="inlineStr"/>
       <c r="F158" s="2" t="inlineStr"/>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>Total number of units</t>
+          <t>The total number of existing units</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5577,7 +5573,7 @@
       <c r="B159" s="2" t="n"/>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>Total existing units</t>
+          <t>Total proposed units</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr"/>
@@ -5585,12 +5581,12 @@
       <c r="F159" s="2" t="inlineStr"/>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>The total number of existing units</t>
+          <t>The total number of proposed units</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I159" s="2" t="inlineStr">
@@ -5604,7 +5600,7 @@
       <c r="B160" s="2" t="n"/>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Total proposed units</t>
+          <t>Net change</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr"/>
@@ -5612,12 +5608,12 @@
       <c r="F160" s="2" t="inlineStr"/>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>The total number of proposed units</t>
+          <t>Calculated net change in units</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I160" s="2" t="inlineStr">
@@ -5627,11 +5623,19 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="2" t="n"/>
-      <c r="B161" s="2" t="n"/>
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>Site area</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>How big the site is including relevant measurements</t>
+        </is>
+      </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>Net change</t>
+          <t>Site area in hectares</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr"/>
@@ -5639,12 +5643,12 @@
       <c r="F161" s="2" t="inlineStr"/>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>Calculated net change in units</t>
+          <t>The size of the site in hectares</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I161" s="2" t="inlineStr">
@@ -5654,19 +5658,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="2" t="inlineStr">
-        <is>
-          <t>Site area</t>
-        </is>
-      </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>How big the site is including relevant measurements</t>
-        </is>
-      </c>
+      <c r="A162" s="2" t="n"/>
+      <c r="B162" s="2" t="n"/>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>Site area in hectares</t>
+          <t>Site area provided by</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr"/>
@@ -5674,39 +5670,51 @@
       <c r="F162" s="2" t="inlineStr"/>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>The size of the site in hectares</t>
+          <t>Who provided the site area value</t>
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="2" t="n"/>
-      <c r="B163" s="2" t="n"/>
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>Site details</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>Where the proposed development will be built.</t>
+        </is>
+      </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>Site area provided by</t>
-        </is>
-      </c>
-      <c r="D163" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>Site boundary</t>
+        </is>
+      </c>
       <c r="E163" s="2" t="inlineStr"/>
       <c r="F163" s="2" t="inlineStr"/>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>Who provided the site area value</t>
+          <t>Geometry of the site of the development, typically in GeoJSON format</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>wkt</t>
         </is>
       </c>
       <c r="I163" s="2" t="inlineStr">
@@ -5716,16 +5724,8 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="2" t="inlineStr">
-        <is>
-          <t>Site details</t>
-        </is>
-      </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>Where the proposed development will be built.</t>
-        </is>
-      </c>
+      <c r="A164" s="2" t="n"/>
+      <c r="B164" s="2" t="n"/>
       <c r="C164" s="2" t="inlineStr">
         <is>
           <t>Site locations[]</t>
@@ -5733,19 +5733,19 @@
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>Site boundary</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr"/>
       <c r="F164" s="2" t="inlineStr"/>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>Geometry of the site of the development, typically in GeoJSON format</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t>wkt</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I164" s="2" t="inlineStr">
@@ -5764,14 +5764,14 @@
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr"/>
       <c r="F165" s="2" t="inlineStr"/>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
@@ -5795,19 +5795,19 @@
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Easting</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr"/>
       <c r="F166" s="2" t="inlineStr"/>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I166" s="2" t="inlineStr">
@@ -5826,19 +5826,19 @@
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>Easting</t>
+          <t>Northing</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr"/>
       <c r="F167" s="2" t="inlineStr"/>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
+          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I167" s="2" t="inlineStr">
@@ -5857,19 +5857,19 @@
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>Northing</t>
+          <t>Latitude</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr"/>
       <c r="F168" s="2" t="inlineStr"/>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
+          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="I168" s="2" t="inlineStr">
@@ -5888,19 +5888,19 @@
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>Latitude</t>
+          <t>Longitude</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr"/>
       <c r="F169" s="2" t="inlineStr"/>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="I169" s="2" t="inlineStr">
@@ -5919,19 +5919,19 @@
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>Longitude</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr"/>
       <c r="F170" s="2" t="inlineStr"/>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>A text description providing details about the subject.</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I170" s="2" t="inlineStr">
@@ -5950,14 +5950,14 @@
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>UPRNs[]</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr"/>
       <c r="F171" s="2" t="inlineStr"/>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>A text description providing details about the subject. For parking changes, this describes how the proposed works affect existing car parking arrangements.</t>
+          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
@@ -5972,50 +5972,46 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="2" t="n"/>
-      <c r="B172" s="2" t="n"/>
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>Site Visit Details</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>Information to help the planning authority arrange a site visit</t>
+        </is>
+      </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="D172" s="2" t="inlineStr">
-        <is>
-          <t>UPRNs[]</t>
-        </is>
-      </c>
+          <t>Site seen from public area</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr"/>
       <c r="E172" s="2" t="inlineStr"/>
       <c r="F172" s="2" t="inlineStr"/>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
+          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="2" t="inlineStr">
-        <is>
-          <t>Site Visit Details</t>
-        </is>
-      </c>
-      <c r="B173" s="2" t="inlineStr">
-        <is>
-          <t>Information to help the planning authority arrange a site visit</t>
-        </is>
-      </c>
+      <c r="A173" s="2" t="n"/>
+      <c r="B173" s="2" t="n"/>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>Site seen from public area</t>
+          <t>Site visit contact type</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr"/>
@@ -6023,12 +6019,12 @@
       <c r="F173" s="2" t="inlineStr"/>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
+          <t>Indicates who the authority should contact to arrange a site visit</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I173" s="2" t="inlineStr">
@@ -6042,7 +6038,7 @@
       <c r="B174" s="2" t="n"/>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>Site visit contact type</t>
+          <t>Contact reference</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr"/>
@@ -6050,17 +6046,17 @@
       <c r="F174" s="2" t="inlineStr"/>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>Indicates who the authority should contact to arrange a site visit</t>
+          <t>The reference of the applicant or agent who should be contacted for site visits</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I174" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -6069,15 +6065,19 @@
       <c r="B175" s="2" t="n"/>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>Contact reference</t>
-        </is>
-      </c>
-      <c r="D175" s="2" t="inlineStr"/>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Full name</t>
+        </is>
+      </c>
       <c r="E175" s="2" t="inlineStr"/>
       <c r="F175" s="2" t="inlineStr"/>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+          <t>The complete name of a person</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr">
@@ -6087,7 +6087,7 @@
       </c>
       <c r="I175" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -6101,14 +6101,14 @@
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>Full name</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr"/>
       <c r="F176" s="2" t="inlineStr"/>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>The complete name of a person</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
@@ -6132,14 +6132,14 @@
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr"/>
       <c r="F177" s="2" t="inlineStr"/>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
@@ -6148,37 +6148,6 @@
         </is>
       </c>
       <c r="I177" s="2" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="2" t="n"/>
-      <c r="B178" s="2" t="n"/>
-      <c r="C178" s="2" t="inlineStr">
-        <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="D178" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="E178" s="2" t="inlineStr"/>
-      <c r="F178" s="2" t="inlineStr"/>
-      <c r="G178" s="2" t="inlineStr">
-        <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
-        </is>
-      </c>
-      <c r="H178" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="I178" s="2" t="inlineStr">
         <is>
           <t>MUST</t>
         </is>
@@ -6186,50 +6155,50 @@
     </row>
   </sheetData>
   <mergeCells count="44">
-    <mergeCell ref="B35:B40"/>
-    <mergeCell ref="A68:A77"/>
-    <mergeCell ref="B31:B34"/>
-    <mergeCell ref="B146:B161"/>
-    <mergeCell ref="B109:B123"/>
-    <mergeCell ref="B55"/>
-    <mergeCell ref="A164:A172"/>
-    <mergeCell ref="B124:B128"/>
-    <mergeCell ref="B84:B90"/>
-    <mergeCell ref="B140:B145"/>
-    <mergeCell ref="A162:A163"/>
-    <mergeCell ref="B2:B18"/>
-    <mergeCell ref="A59:A61"/>
-    <mergeCell ref="B62:B67"/>
-    <mergeCell ref="A78:A83"/>
-    <mergeCell ref="A91:A108"/>
-    <mergeCell ref="A129:A139"/>
-    <mergeCell ref="B56:B58"/>
-    <mergeCell ref="B41:B54"/>
-    <mergeCell ref="B19:B22"/>
-    <mergeCell ref="B59:B61"/>
-    <mergeCell ref="B162:B163"/>
-    <mergeCell ref="B23:B30"/>
-    <mergeCell ref="A173:A178"/>
-    <mergeCell ref="B164:B172"/>
-    <mergeCell ref="B78:B83"/>
-    <mergeCell ref="B91:B108"/>
-    <mergeCell ref="A2:A18"/>
-    <mergeCell ref="B129:B139"/>
-    <mergeCell ref="A109:A123"/>
-    <mergeCell ref="A19:A22"/>
-    <mergeCell ref="A146:A161"/>
-    <mergeCell ref="A35:A40"/>
-    <mergeCell ref="A124:A128"/>
-    <mergeCell ref="A84:A90"/>
-    <mergeCell ref="A31:A34"/>
-    <mergeCell ref="A140:A145"/>
-    <mergeCell ref="A55"/>
-    <mergeCell ref="A41:A54"/>
-    <mergeCell ref="B68:B77"/>
-    <mergeCell ref="A23:A30"/>
-    <mergeCell ref="B173:B178"/>
-    <mergeCell ref="A56:A58"/>
-    <mergeCell ref="A62:A67"/>
+    <mergeCell ref="A145:A160"/>
+    <mergeCell ref="A57:A59"/>
+    <mergeCell ref="A42:A55"/>
+    <mergeCell ref="A2:A19"/>
+    <mergeCell ref="A24:A31"/>
+    <mergeCell ref="A36:A41"/>
+    <mergeCell ref="A172:A177"/>
+    <mergeCell ref="A79:A84"/>
+    <mergeCell ref="B161:B162"/>
+    <mergeCell ref="A163:A171"/>
+    <mergeCell ref="B92:B107"/>
+    <mergeCell ref="A85:A91"/>
+    <mergeCell ref="A108:A122"/>
+    <mergeCell ref="A92:A107"/>
+    <mergeCell ref="B123:B127"/>
+    <mergeCell ref="A69:A78"/>
+    <mergeCell ref="B128:B138"/>
+    <mergeCell ref="B63:B68"/>
+    <mergeCell ref="A32:A35"/>
+    <mergeCell ref="A123:A127"/>
+    <mergeCell ref="B56"/>
+    <mergeCell ref="A139:A144"/>
+    <mergeCell ref="A60:A62"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="B85:B91"/>
+    <mergeCell ref="B172:B177"/>
+    <mergeCell ref="B108:B122"/>
+    <mergeCell ref="B69:B78"/>
+    <mergeCell ref="B163:B171"/>
+    <mergeCell ref="B145:B160"/>
+    <mergeCell ref="B36:B41"/>
+    <mergeCell ref="A56"/>
+    <mergeCell ref="B57:B59"/>
+    <mergeCell ref="A161:A162"/>
+    <mergeCell ref="B139:B144"/>
+    <mergeCell ref="B20:B23"/>
+    <mergeCell ref="B42:B55"/>
+    <mergeCell ref="B60:B62"/>
+    <mergeCell ref="A63:A68"/>
+    <mergeCell ref="B2:B19"/>
+    <mergeCell ref="B24:B31"/>
+    <mergeCell ref="B32:B35"/>
+    <mergeCell ref="A128:A138"/>
+    <mergeCell ref="B79:B84"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/generated/spreadsheet/outline-planning-outline.xlsx
+++ b/generated/spreadsheet/outline-planning-outline.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I177"/>
+  <dimension ref="A1:I180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -437,7 +437,7 @@
     <col width="29" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="72" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -1413,13 +1413,17 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>Address Text</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1448,13 +1452,17 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>Postcode</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr"/>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1478,14 +1486,22 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr"/>
-      <c r="F30" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>UPRN</t>
+        </is>
+      </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>The name of a company (that the agent works for)</t>
+          <t>Unique Property Reference Number for a property</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -1509,19 +1525,19 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>User role</t>
+          <t>Company</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr"/>
       <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>The role of the named individual. Agent or proxy</t>
+          <t>The name of a company (that the agent works for)</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -1531,58 +1547,58 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>Applicant contact details</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>Telephone number and email address of the applicant.</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="n"/>
+      <c r="B32" s="2" t="n"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Applicant reference</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr"/>
+          <t>agent</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>User role</t>
+        </is>
+      </c>
       <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Reference to match contact details to a named individual from the applicant details component</t>
+          <t>The role of the named individual. Agent or proxy</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n"/>
-      <c r="B33" s="2" t="n"/>
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Applicant contact details</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Telephone number and email address of the applicant.</t>
+        </is>
+      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Applicant reference</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr"/>
       <c r="E33" s="2" t="inlineStr"/>
       <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>Reference to match contact details to a named individual from the applicant details component</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -1606,18 +1622,14 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -1627,7 +1639,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1646,18 +1658,18 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Contact priority</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -1667,47 +1679,51 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>Applicant details</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>Name and contact information for the parties making the application.</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="n"/>
+      <c r="B36" s="2" t="n"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Applicants[]</t>
+          <t>Contact details</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Contact priority</t>
+        </is>
+      </c>
       <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n"/>
-      <c r="B37" s="2" t="n"/>
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Applicant details</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information for the parties making the application.</t>
+        </is>
+      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>Applicants[]</t>
@@ -1715,18 +1731,14 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr"/>
       <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -1736,7 +1748,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1755,13 +1767,13 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr"/>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -1771,7 +1783,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1790,13 +1802,13 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr"/>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -1825,13 +1837,13 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -1860,58 +1872,66 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Text representation of an address or site</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n"/>
+      <c r="B42" s="2" t="n"/>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Applicants[]</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
           <t>Postcode</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr"/>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>The postal code</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>MAY</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>Biodiversity net gain</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>How any natural habitats on the development site will be improved by the proposed works.</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Biodiversity gain condition applies</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr"/>
-      <c r="E42" s="2" t="inlineStr"/>
-      <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Does the applicant believe the Biodiversity Gain Condition applies to this application</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1920,55 +1940,67 @@
       <c r="B43" s="2" t="n"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity gain condition exemption reason[]</t>
+          <t>Applicants[]</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Exemption type</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr"/>
-      <c r="F43" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>UPRN</t>
+        </is>
+      </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>The type of biodiversity gain exemption from the bng-exemption-type enum</t>
+          <t>Unique Property Reference Number for a property</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n"/>
-      <c r="B44" s="2" t="n"/>
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Biodiversity net gain</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>How any natural habitats on the development site will be improved by the proposed works.</t>
+        </is>
+      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity gain condition exemption reason[]</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>Reason</t>
-        </is>
-      </c>
+          <t>Biodiversity gain condition applies</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr"/>
       <c r="E44" s="2" t="inlineStr"/>
       <c r="F44" s="2" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>The reason the exemption applies to this proposal</t>
+          <t>Does the applicant believe the Biodiversity Gain Condition applies to this application</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -1982,24 +2014,24 @@
       <c r="B45" s="2" t="n"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity net gain details</t>
+          <t>Biodiversity gain condition exemption reason[]</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Pre development date</t>
+          <t>Exemption type</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
       <c r="F45" s="2" t="inlineStr"/>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Date of pre-development biodiversity value calculation, must align with application or justified earlier date</t>
+          <t>The type of biodiversity gain exemption from the bng-exemption-type enum</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
@@ -2013,24 +2045,24 @@
       <c r="B46" s="2" t="n"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity net gain details</t>
+          <t>Biodiversity gain condition exemption reason[]</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Pre development biodiversity value</t>
+          <t>Reason</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr"/>
       <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Calculated biodiversity value in Habitat Biodiversity Units</t>
+          <t>The reason the exemption applies to this proposal</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -2049,24 +2081,24 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Earlier date reason</t>
+          <t>Pre development date</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr"/>
       <c r="F47" s="2" t="inlineStr"/>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Reason for using a pre-development date that is earlier than the application submission</t>
+          <t>Date of pre-development biodiversity value calculation, must align with application or justified earlier date</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2080,24 +2112,24 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Habitat loss after 2020</t>
+          <t>Pre development biodiversity value</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr"/>
       <c r="F48" s="2" t="inlineStr"/>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether there has been degradation of onsite habitat(s) after 30 Jan 2020</t>
+          <t>Calculated biodiversity value in Habitat Biodiversity Units</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2111,28 +2143,24 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Habitat loss details</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>Loss date</t>
-        </is>
-      </c>
+          <t>Earlier date reason</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr"/>
       <c r="F49" s="2" t="inlineStr"/>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Date the activity causing habitat loss or degradation occurred</t>
+          <t>Reason for using a pre-development date that is earlier than the application submission</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2146,28 +2174,24 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Habitat loss details</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>Pre loss biodiversity value</t>
-        </is>
-      </c>
+          <t>Habitat loss after 2020</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr"/>
       <c r="F50" s="2" t="inlineStr"/>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity value immediately before habitat loss or degradation occurred, measured in Habitat Biodiversity Units</t>
+          <t>Indicates whether there has been degradation of onsite habitat(s) after 30 Jan 2020</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2186,23 +2210,23 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Supporting evidence</t>
+          <t>Loss date</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr"/>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Description or reference to supporting documents for habitat loss or degradation evidence</t>
+          <t>Date the activity causing habitat loss or degradation occurred</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2216,19 +2240,23 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Metric publication date</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr"/>
+          <t>Habitat loss details</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Pre loss biodiversity value</t>
+        </is>
+      </c>
       <c r="F52" s="2" t="inlineStr"/>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Publication date of the biodiversity metric tool used for calculations</t>
+          <t>Biodiversity value immediately before habitat loss or degradation occurred, measured in Habitat Biodiversity Units</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
@@ -2247,24 +2275,28 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Irreplaceable habitats</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr"/>
+          <t>Habitat loss details</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Supporting evidence</t>
+        </is>
+      </c>
       <c r="F53" s="2" t="inlineStr"/>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether the site contains any irreplaceable habitats</t>
+          <t>Description or reference to supporting documents for habitat loss or degradation evidence</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2278,24 +2310,24 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Irreplaceable habitats details</t>
+          <t>Metric publication date</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr"/>
       <c r="F54" s="2" t="inlineStr"/>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Description and references for any irreplaceable habitats identified on the site</t>
+          <t>Publication date of the biodiversity metric tool used for calculations</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2309,23 +2341,19 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Irreplaceable habitats</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr"/>
       <c r="F55" s="2" t="inlineStr"/>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Indicates whether the site contains any irreplaceable habitats</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
@@ -2335,27 +2363,23 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>Checklist</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="n"/>
+      <c r="B56" s="2" t="n"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>National requirement types[]</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr"/>
+          <t>Biodiversity net gain details</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Irreplaceable habitats details</t>
+        </is>
+      </c>
       <c r="E56" s="2" t="inlineStr"/>
       <c r="F56" s="2" t="inlineStr"/>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>List of the document types required for the given application type</t>
+          <t>Description and references for any irreplaceable habitats identified on the site</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -2365,37 +2389,37 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>Conflict of interest</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
-        </is>
-      </c>
+      <c r="A57" s="2" t="n"/>
+      <c r="B57" s="2" t="n"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Conflict to declare</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr"/>
-      <c r="E57" s="2" t="inlineStr"/>
+          <t>Biodiversity net gain details</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="F57" s="2" t="inlineStr"/>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
@@ -2405,11 +2429,19 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n"/>
-      <c r="B58" s="2" t="n"/>
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Checklist</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
+        </is>
+      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Person reference</t>
+          <t>National requirement types[]</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr"/>
@@ -2417,7 +2449,7 @@
       <c r="F58" s="2" t="inlineStr"/>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Reference to the applicant or agent with the conflict</t>
+          <t>List of the document types required for the given application type</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -2427,16 +2459,24 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n"/>
-      <c r="B59" s="2" t="n"/>
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Conflict of interest</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
+        </is>
+      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Conflict details</t>
+          <t>Conflict to declare</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr"/>
@@ -2444,31 +2484,23 @@
       <c r="F59" s="2" t="inlineStr"/>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
+          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>Declaration</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>Signed and dated verification of the application's accuracy.</t>
-        </is>
-      </c>
+      <c r="A60" s="2" t="n"/>
+      <c r="B60" s="2" t="n"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>Person reference</t>
@@ -2479,7 +2511,7 @@
       <c r="F60" s="2" t="inlineStr"/>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Declaration must be made by an applicant or agent making the application</t>
+          <t>Reference to the applicant or agent with the conflict</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -2489,7 +2521,7 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2530,7 @@
       <c r="B61" s="2" t="n"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
+          <t>Conflict details</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr"/>
@@ -2506,26 +2538,34 @@
       <c r="F61" s="2" t="inlineStr"/>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n"/>
-      <c r="B62" s="2" t="n"/>
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Declaration</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Signed and dated verification of the application's accuracy.</t>
+        </is>
+      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr"/>
@@ -2533,12 +2573,12 @@
       <c r="F62" s="2" t="inlineStr"/>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Declaration must be made by an applicant or agent making the application</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
@@ -2548,36 +2588,24 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>Employment</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>How the proposed development will impact existing and proposed employee numbers</t>
-        </is>
-      </c>
+      <c r="A63" s="2" t="n"/>
+      <c r="B63" s="2" t="n"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Existing employees</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>Full-time</t>
-        </is>
-      </c>
+          <t>Declaration confirmed</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr"/>
       <c r="E63" s="2" t="inlineStr"/>
       <c r="F63" s="2" t="inlineStr"/>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Number of full-time employees</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
@@ -2591,24 +2619,20 @@
       <c r="B64" s="2" t="n"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Existing employees</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>Part-time</t>
-        </is>
-      </c>
+          <t>Declaration date</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr"/>
       <c r="E64" s="2" t="inlineStr"/>
       <c r="F64" s="2" t="inlineStr"/>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Number of part-time employees</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
@@ -2618,8 +2642,16 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n"/>
-      <c r="B65" s="2" t="n"/>
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Employment</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>How the proposed development will impact existing and proposed employee numbers</t>
+        </is>
+      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>Existing employees</t>
@@ -2627,19 +2659,19 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Total FTE</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr"/>
       <c r="F65" s="2" t="inlineStr"/>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Total full-time equivalent (FTE)</t>
+          <t>Number of full-time employees</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
@@ -2653,19 +2685,19 @@
       <c r="B66" s="2" t="n"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Proposed employees</t>
+          <t>Existing employees</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Part-time</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr"/>
       <c r="F66" s="2" t="inlineStr"/>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Number of full-time employees</t>
+          <t>Number of part-time employees</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -2684,24 +2716,24 @@
       <c r="B67" s="2" t="n"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Proposed employees</t>
+          <t>Existing employees</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Part-time</t>
+          <t>Total FTE</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr"/>
       <c r="F67" s="2" t="inlineStr"/>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Number of part-time employees</t>
+          <t>Total full-time equivalent (FTE)</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
@@ -2720,19 +2752,19 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Total FTE</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr"/>
       <c r="F68" s="2" t="inlineStr"/>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Total full-time equivalent (FTE)</t>
+          <t>Number of full-time employees</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
@@ -2742,36 +2774,28 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>Existing use</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>How the site is currently being used.</t>
-        </is>
-      </c>
+      <c r="A69" s="2" t="n"/>
+      <c r="B69" s="2" t="n"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Existing use details[]</t>
+          <t>Proposed employees</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Use</t>
+          <t>Part-time</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr"/>
       <c r="F69" s="2" t="inlineStr"/>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>A use class or type of use</t>
+          <t>Number of part-time employees</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
@@ -2785,35 +2809,43 @@
       <c r="B70" s="2" t="n"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Existing use details[]</t>
+          <t>Proposed employees</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Use details</t>
+          <t>Total FTE</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr"/>
       <c r="F70" s="2" t="inlineStr"/>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Further detail of the use</t>
+          <t>Total full-time equivalent (FTE)</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n"/>
-      <c r="B71" s="2" t="n"/>
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Existing use</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>How the site is currently being used.</t>
+        </is>
+      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>Existing use details[]</t>
@@ -2821,19 +2853,19 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Land part</t>
+          <t>Use</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr"/>
       <c r="F71" s="2" t="inlineStr"/>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Which part of the land the use relates to</t>
+          <t>A use class or type of use</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
@@ -2847,25 +2879,29 @@
       <c r="B72" s="2" t="n"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Site vacant</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr"/>
+          <t>Existing use details[]</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Use details</t>
+        </is>
+      </c>
       <c r="E72" s="2" t="inlineStr"/>
       <c r="F72" s="2" t="inlineStr"/>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Is the site currently vacant</t>
+          <t>Further detail of the use</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2874,15 +2910,19 @@
       <c r="B73" s="2" t="n"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Last use details</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr"/>
+          <t>Existing use details[]</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Land part</t>
+        </is>
+      </c>
       <c r="E73" s="2" t="inlineStr"/>
       <c r="F73" s="2" t="inlineStr"/>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Description of the last use of the site</t>
+          <t>Which part of the land the use relates to</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -2892,7 +2932,7 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2941,7 @@
       <c r="B74" s="2" t="n"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Last use end date</t>
+          <t>Site vacant</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr"/>
@@ -2909,17 +2949,17 @@
       <c r="F74" s="2" t="inlineStr"/>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Date the last use ended (YYYY-MM-DD format)</t>
+          <t>Is the site currently vacant</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2968,7 @@
       <c r="B75" s="2" t="n"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Is contaminated land</t>
+          <t>Last use details</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr"/>
@@ -2936,17 +2976,17 @@
       <c r="F75" s="2" t="inlineStr"/>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Is the site known to be contaminated?</t>
+          <t>Description of the last use of the site</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2955,7 +2995,7 @@
       <c r="B76" s="2" t="n"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Is suspected contaminated land</t>
+          <t>Last use end date</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr"/>
@@ -2963,17 +3003,17 @@
       <c r="F76" s="2" t="inlineStr"/>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Is the site suspected of contamination?</t>
+          <t>Date the last use ended (YYYY-MM-DD format)</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2982,7 +3022,7 @@
       <c r="B77" s="2" t="n"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Proposed use contamination risk</t>
+          <t>Is contaminated land</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr"/>
@@ -2990,7 +3030,7 @@
       <c r="F77" s="2" t="inlineStr"/>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>Is the proposed use vulnerable to the presence of contamination?</t>
+          <t>Is the site known to be contaminated?</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -3009,7 +3049,7 @@
       <c r="B78" s="2" t="n"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Contamination assessment</t>
+          <t>Is suspected contaminated land</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr"/>
@@ -3017,34 +3057,26 @@
       <c r="F78" s="2" t="inlineStr"/>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Reference to contamination assessment document</t>
+          <t>Is the site suspected of contamination?</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>Flood risk assessment</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>Results of any flood risk assessments made for the development site</t>
-        </is>
-      </c>
+      <c r="A79" s="2" t="n"/>
+      <c r="B79" s="2" t="n"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Flood risk area</t>
+          <t>Proposed use contamination risk</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr"/>
@@ -3052,7 +3084,7 @@
       <c r="F79" s="2" t="inlineStr"/>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Is the site within an area at risk of flooding?</t>
+          <t>Is the proposed use vulnerable to the presence of contamination?</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -3071,7 +3103,7 @@
       <c r="B80" s="2" t="n"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Data provided by</t>
+          <t>Contamination assessment</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr"/>
@@ -3079,12 +3111,12 @@
       <c r="F80" s="2" t="inlineStr"/>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Who provided the data: Applicant or System/Service?</t>
+          <t>Reference to contamination assessment document</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
@@ -3094,11 +3126,19 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n"/>
-      <c r="B81" s="2" t="n"/>
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>Flood risk assessment</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Results of any flood risk assessments made for the development site</t>
+        </is>
+      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Flood risk assessment</t>
+          <t>Flood risk area</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr"/>
@@ -3106,17 +3146,17 @@
       <c r="F81" s="2" t="inlineStr"/>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Reference of the flood risk assessment document</t>
+          <t>Is the site within an area at risk of flooding?</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3165,7 @@
       <c r="B82" s="2" t="n"/>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Within 20m watercourse</t>
+          <t>Data provided by</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr"/>
@@ -3133,17 +3173,17 @@
       <c r="F82" s="2" t="inlineStr"/>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Whether the development is within 20 metres of a watercourse</t>
+          <t>Who provided the data: Applicant or System/Service?</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3192,7 @@
       <c r="B83" s="2" t="n"/>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Increases flood risk</t>
+          <t>Flood risk assessment</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr"/>
@@ -3160,17 +3200,17 @@
       <c r="F83" s="2" t="inlineStr"/>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Whether the development increases flood risk</t>
+          <t>Reference of the flood risk assessment document</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3179,7 +3219,7 @@
       <c r="B84" s="2" t="n"/>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Surface water disposal[]</t>
+          <t>Within 20m watercourse</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr"/>
@@ -3187,12 +3227,12 @@
       <c r="F84" s="2" t="inlineStr"/>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Method for disposing of surface water</t>
+          <t>Whether the development is within 20 metres of a watercourse</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
@@ -3202,36 +3242,24 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>Hours of operation</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>Proposed operating hours if the proposed development is intended for non-residential use.</t>
-        </is>
-      </c>
+      <c r="A85" s="2" t="n"/>
+      <c r="B85" s="2" t="n"/>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Hours of operation[]</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>Use</t>
-        </is>
-      </c>
+          <t>Increases flood risk</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr"/>
       <c r="E85" s="2" t="inlineStr"/>
       <c r="F85" s="2" t="inlineStr"/>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>A use class or type of use</t>
+          <t>Whether the development increases flood risk</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
@@ -3245,35 +3273,39 @@
       <c r="B86" s="2" t="n"/>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Hours of operation[]</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t>Use other</t>
-        </is>
-      </c>
+          <t>Surface water disposal[]</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr"/>
       <c r="E86" s="2" t="inlineStr"/>
       <c r="F86" s="2" t="inlineStr"/>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Specify use if use is "other"</t>
+          <t>Method for disposing of surface water</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n"/>
-      <c r="B87" s="2" t="n"/>
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Hours of operation</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>Proposed operating hours if the proposed development is intended for non-residential use.</t>
+        </is>
+      </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
           <t>Hours of operation[]</t>
@@ -3281,18 +3313,14 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Operational times[]</t>
-        </is>
-      </c>
-      <c r="E87" s="2" t="inlineStr">
-        <is>
-          <t>Schedule days[]</t>
-        </is>
-      </c>
+          <t>Use</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr"/>
       <c r="F87" s="2" t="inlineStr"/>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>List of days or day categories that a schedule entry applies to</t>
+          <t>A use class or type of use</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -3316,23 +3344,19 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Operational times[]</t>
-        </is>
-      </c>
-      <c r="E88" s="2" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
+          <t>Use other</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr"/>
       <c r="F88" s="2" t="inlineStr"/>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>True or False - explicitly state when closed</t>
+          <t>Specify use if use is "other"</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
@@ -3356,22 +3380,18 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Time ranges[]</t>
-        </is>
-      </c>
-      <c r="F89" s="2" t="inlineStr">
-        <is>
-          <t>Open time</t>
-        </is>
-      </c>
+          <t>Schedule days[]</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr"/>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Opening time</t>
+          <t>List of days or day categories that a schedule entry applies to</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
@@ -3395,27 +3415,23 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Time ranges[]</t>
-        </is>
-      </c>
-      <c r="F90" s="2" t="inlineStr">
-        <is>
-          <t>Close time</t>
-        </is>
-      </c>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr"/>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Closing time</t>
+          <t>True or False - explicitly state when closed</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3429,54 +3445,66 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Hours not known</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr"/>
-      <c r="F91" s="2" t="inlineStr"/>
+          <t>Operational times[]</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>Time ranges[]</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>Open time</t>
+        </is>
+      </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Applicant states they do not know the hours of operation</t>
+          <t>Opening time</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>Non residential floorspace</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>Details of changes to non-residential floorspace in the proposed development.</t>
-        </is>
-      </c>
+      <c r="A92" s="2" t="n"/>
+      <c r="B92" s="2" t="n"/>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Non residential change</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr"/>
-      <c r="E92" s="2" t="inlineStr"/>
-      <c r="F92" s="2" t="inlineStr"/>
+          <t>Hours of operation[]</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Operational times[]</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>Time ranges[]</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>Close time</t>
+        </is>
+      </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Does the proposal involve the loss, gain, or change of non-residential floorspace?</t>
+          <t>Closing time</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
@@ -3490,60 +3518,64 @@
       <c r="B93" s="2" t="n"/>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Floorspace details[]</t>
+          <t>Hours of operation[]</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Use</t>
+          <t>Hours not known</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr"/>
       <c r="F93" s="2" t="inlineStr"/>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>A use class or type of use</t>
+          <t>Applicant states they do not know the hours of operation</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n"/>
-      <c r="B94" s="2" t="n"/>
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Non residential floorspace</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Details of changes to non-residential floorspace in the proposed development.</t>
+        </is>
+      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Floorspace details[]</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
-        <is>
-          <t>Specified use</t>
-        </is>
-      </c>
+          <t>Non residential change</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr"/>
       <c r="E94" s="2" t="inlineStr"/>
       <c r="F94" s="2" t="inlineStr"/>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>A specified use if no applicable use class is available</t>
+          <t>Does the proposal involve the loss, gain, or change of non-residential floorspace?</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3557,19 +3589,19 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Existing gross floorspace</t>
+          <t>Use</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr"/>
       <c r="F95" s="2" t="inlineStr"/>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>Existing gross internal floorspace, in sqm</t>
+          <t>A use class or type of use</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
@@ -3588,19 +3620,19 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Is floorspace lost known</t>
+          <t>Specified use</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr"/>
       <c r="F96" s="2" t="inlineStr"/>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Whether the amount of floorspace to be lost is known</t>
+          <t>A specified use if no applicable use class is available</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
@@ -3619,14 +3651,14 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Floorspace lost</t>
+          <t>Existing gross floorspace</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr"/>
       <c r="F97" s="2" t="inlineStr"/>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>Gross floorspace to be lost by change of use, in sqm</t>
+          <t>Existing gross internal floorspace, in sqm</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -3636,7 +3668,7 @@
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3650,14 +3682,14 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Is total gross proposed known</t>
+          <t>Is floorspace lost known</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr"/>
       <c r="F98" s="2" t="inlineStr"/>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Whether the total gross proposed floorspace is known</t>
+          <t>Whether the amount of floorspace to be lost is known</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -3681,14 +3713,14 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Total gross proposed</t>
+          <t>Floorspace lost</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr"/>
       <c r="F99" s="2" t="inlineStr"/>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Total gross internal floorspace proposed, in sqm</t>
+          <t>Gross floorspace to be lost by change of use, in sqm</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -3712,24 +3744,24 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Net additional floorspace</t>
+          <t>Is total gross proposed known</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr"/>
       <c r="F100" s="2" t="inlineStr"/>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Net additional gross internal floorspace, in sqm</t>
+          <t>Whether the total gross proposed floorspace is known</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3738,29 +3770,29 @@
       <c r="B101" s="2" t="n"/>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Room details[]</t>
+          <t>Floorspace details[]</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Use class for accommodation</t>
+          <t>Total gross proposed</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr"/>
       <c r="F101" s="2" t="inlineStr"/>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Type of non-residential use class referring to accommodation uses</t>
+          <t>Total gross internal floorspace proposed, in sqm</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3769,29 +3801,29 @@
       <c r="B102" s="2" t="n"/>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Room details[]</t>
+          <t>Floorspace details[]</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Use other</t>
+          <t>Net additional floorspace</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr"/>
       <c r="F102" s="2" t="inlineStr"/>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>Specify use if use is "other"</t>
+          <t>Net additional gross internal floorspace, in sqm</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3805,24 +3837,24 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Is existing rooms lost known</t>
+          <t>Use class for accommodation</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr"/>
       <c r="F103" s="2" t="inlineStr"/>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>Whether the total existing rooms that will be lost is known</t>
+          <t>Type of non-residential use class referring to accommodation uses</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3836,19 +3868,19 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Existing rooms lost</t>
+          <t>Use other</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr"/>
       <c r="F104" s="2" t="inlineStr"/>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>Existing rooms to be lost by change of use</t>
+          <t>Specify use if use is "other"</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
@@ -3867,14 +3899,14 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Is total rooms proposed known</t>
+          <t>Is existing rooms lost known</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr"/>
       <c r="F105" s="2" t="inlineStr"/>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>Whether the total rooms proposed is known</t>
+          <t>Whether the total existing rooms that will be lost is known</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -3898,14 +3930,14 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Total rooms proposed</t>
+          <t>Existing rooms lost</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr"/>
       <c r="F106" s="2" t="inlineStr"/>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Total rooms proposed (including change of use)</t>
+          <t>Existing rooms to be lost by change of use</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -3929,59 +3961,55 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Net additional rooms</t>
+          <t>Is total rooms proposed known</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr"/>
       <c r="F107" s="2" t="inlineStr"/>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Net additional rooms following development</t>
+          <t>Whether the total rooms proposed is known</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="inlineStr">
-        <is>
-          <t>Ownership certificates and agricultural land declaration</t>
-        </is>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
-        </is>
-      </c>
+      <c r="A108" s="2" t="n"/>
+      <c r="B108" s="2" t="n"/>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Sole owner</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr"/>
+          <t>Room details[]</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Total rooms proposed</t>
+        </is>
+      </c>
       <c r="E108" s="2" t="inlineStr"/>
       <c r="F108" s="2" t="inlineStr"/>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Is the applicant the sole owner of the land?</t>
+          <t>Total rooms proposed (including change of use)</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3990,20 +4018,24 @@
       <c r="B109" s="2" t="n"/>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Agricultural tenants</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr"/>
+          <t>Room details[]</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Net additional rooms</t>
+        </is>
+      </c>
       <c r="E109" s="2" t="inlineStr"/>
       <c r="F109" s="2" t="inlineStr"/>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>Are there any agricultural tenants on the land?</t>
+          <t>Net additional rooms following development</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
@@ -4013,37 +4045,37 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="n"/>
-      <c r="B110" s="2" t="n"/>
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>Ownership certificates and agricultural land declaration</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
+        </is>
+      </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Owners and tenants[]</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E110" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Sole owner</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr"/>
+      <c r="E110" s="2" t="inlineStr"/>
       <c r="F110" s="2" t="inlineStr"/>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>Is the applicant the sole owner of the land?</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4052,28 +4084,20 @@
       <c r="B111" s="2" t="n"/>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Owners and tenants[]</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E111" s="2" t="inlineStr">
-        <is>
-          <t>First Name</t>
-        </is>
-      </c>
+          <t>Agricultural tenants</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr"/>
+      <c r="E111" s="2" t="inlineStr"/>
       <c r="F111" s="2" t="inlineStr"/>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>Are there any agricultural tenants on the land?</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
@@ -4097,13 +4121,13 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr"/>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -4113,7 +4137,7 @@
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4132,13 +4156,13 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr"/>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -4167,13 +4191,13 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr"/>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -4183,7 +4207,7 @@
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4197,24 +4221,32 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Notice served date</t>
-        </is>
-      </c>
-      <c r="E115" s="2" t="inlineStr"/>
-      <c r="F115" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>Date when notice was served</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4223,20 +4255,32 @@
       <c r="B116" s="2" t="n"/>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Ownership certificate type</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr"/>
-      <c r="E116" s="2" t="inlineStr"/>
-      <c r="F116" s="2" t="inlineStr"/>
+          <t>Owners and tenants[]</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>The type of ownership certificate based on ownership and tenancy status</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
@@ -4250,15 +4294,27 @@
       <c r="B117" s="2" t="n"/>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Steps taken</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr"/>
-      <c r="E117" s="2" t="inlineStr"/>
-      <c r="F117" s="2" t="inlineStr"/>
+          <t>Owners and tenants[]</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>UPRN</t>
+        </is>
+      </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>Description of steps taken to identify unknown owners or tenants</t>
+          <t>Unique Property Reference Number for a property</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
@@ -4277,29 +4333,29 @@
       <c r="B118" s="2" t="n"/>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Newspaper notices[]</t>
+          <t>Owners and tenants[]</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Newspaper name</t>
+          <t>Notice served date</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr"/>
       <c r="F118" s="2" t="inlineStr"/>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>Name of the newspaper where notice was published</t>
+          <t>Date when notice was served</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4308,29 +4364,25 @@
       <c r="B119" s="2" t="n"/>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Newspaper notices[]</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
-        <is>
-          <t>Publication date</t>
-        </is>
-      </c>
+          <t>Ownership certificate type</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr"/>
       <c r="E119" s="2" t="inlineStr"/>
       <c r="F119" s="2" t="inlineStr"/>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>Date when the notice was published</t>
+          <t>The type of ownership certificate based on ownership and tenancy status</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4339,7 +4391,7 @@
       <c r="B120" s="2" t="n"/>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Person reference</t>
+          <t>Steps taken</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr"/>
@@ -4347,7 +4399,7 @@
       <c r="F120" s="2" t="inlineStr"/>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Declaration must be made by an applicant or agent making the application</t>
+          <t>Description of steps taken to identify unknown owners or tenants</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -4357,7 +4409,7 @@
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4366,20 +4418,24 @@
       <c r="B121" s="2" t="n"/>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr"/>
+          <t>Newspaper notices[]</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>Newspaper name</t>
+        </is>
+      </c>
       <c r="E121" s="2" t="inlineStr"/>
       <c r="F121" s="2" t="inlineStr"/>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>Name of the newspaper where notice was published</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr">
@@ -4393,15 +4449,19 @@
       <c r="B122" s="2" t="n"/>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr"/>
+          <t>Newspaper notices[]</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Publication date</t>
+        </is>
+      </c>
       <c r="E122" s="2" t="inlineStr"/>
       <c r="F122" s="2" t="inlineStr"/>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Date when the notice was published</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -4416,19 +4476,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="inlineStr">
-        <is>
-          <t>Pre-application advice</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
-        </is>
-      </c>
+      <c r="A123" s="2" t="n"/>
+      <c r="B123" s="2" t="n"/>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>Pre-application advice sought</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr"/>
@@ -4436,12 +4488,12 @@
       <c r="F123" s="2" t="inlineStr"/>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>Whether pre-application advice has been sought from the planning authority</t>
+          <t>Declaration must be made by an applicant or agent making the application</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr">
@@ -4455,7 +4507,7 @@
       <c r="B124" s="2" t="n"/>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Officer name</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr"/>
@@ -4463,17 +4515,17 @@
       <c r="F124" s="2" t="inlineStr"/>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>Name of the planning officer who provided the pre-application advice</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4534,7 @@
       <c r="B125" s="2" t="n"/>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr"/>
@@ -4490,26 +4542,34 @@
       <c r="F125" s="2" t="inlineStr"/>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="n"/>
-      <c r="B126" s="2" t="n"/>
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>Pre-application advice</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>Details of pre-application advice previously received from the planning authority</t>
+        </is>
+      </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Advice date</t>
+          <t>Pre-application advice sought</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr"/>
@@ -4517,17 +4577,17 @@
       <c r="F126" s="2" t="inlineStr"/>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
+          <t>Whether pre-application advice has been sought from the planning authority</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4536,7 +4596,7 @@
       <c r="B127" s="2" t="n"/>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>Advice summary</t>
+          <t>Officer name</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr"/>
@@ -4544,7 +4604,7 @@
       <c r="F127" s="2" t="inlineStr"/>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Summary of the pre-application advice received from the planning authority</t>
+          <t>Name of the planning officer who provided the pre-application advice</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -4559,20 +4619,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="inlineStr">
-        <is>
-          <t>Processes machinery waste</t>
-        </is>
-      </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">How waste will be managed on the site
-</t>
-        </is>
-      </c>
+      <c r="A128" s="2" t="n"/>
+      <c r="B128" s="2" t="n"/>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Site activity details</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr"/>
@@ -4580,7 +4631,7 @@
       <c r="F128" s="2" t="inlineStr"/>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>Description of activities, processes, and end products including site operations, plant, ventilation, and machinery</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
@@ -4590,7 +4641,7 @@
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4599,7 +4650,7 @@
       <c r="B129" s="2" t="n"/>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Proposal waste management</t>
+          <t>Advice date</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr"/>
@@ -4607,17 +4658,17 @@
       <c r="F129" s="2" t="inlineStr"/>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>Whether the proposal involves any waste management facility that is relevant to the proposal</t>
+          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4626,55 +4677,56 @@
       <c r="B130" s="2" t="n"/>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Waste management[]</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
-        <is>
-          <t>Waste management facility type</t>
-        </is>
-      </c>
+          <t>Advice summary</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr"/>
       <c r="E130" s="2" t="inlineStr"/>
       <c r="F130" s="2" t="inlineStr"/>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>Type of waste management facility being described in this entry</t>
+          <t>Summary of the pre-application advice received from the planning authority</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="2" t="n"/>
-      <c r="B131" s="2" t="n"/>
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>Processes machinery waste</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">How waste will be managed on the site
+</t>
+        </is>
+      </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>Waste management[]</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
-        <is>
-          <t>Total capacity</t>
-        </is>
-      </c>
+          <t>Site activity details</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr"/>
       <c r="E131" s="2" t="inlineStr"/>
       <c r="F131" s="2" t="inlineStr"/>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>Total capacity of void in cubic metres (or tonnes/litres)</t>
+          <t>Description of activities, processes, and end products including site operations, plant, ventilation, and machinery</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I131" s="2" t="inlineStr">
@@ -4688,24 +4740,20 @@
       <c r="B132" s="2" t="n"/>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Waste management[]</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
-        <is>
-          <t>Unit type</t>
-        </is>
-      </c>
+          <t>Proposal waste management</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr"/>
       <c r="E132" s="2" t="inlineStr"/>
       <c r="F132" s="2" t="inlineStr"/>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
+          <t>Whether the proposal involves any waste management facility that is relevant to the proposal</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr">
@@ -4724,19 +4772,19 @@
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>Annual throughput</t>
+          <t>Waste management facility type</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr"/>
       <c r="F133" s="2" t="inlineStr"/>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>Maximum annual operational throughput in tonnes/litres</t>
+          <t>Type of waste management facility being described in this entry</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I133" s="2" t="inlineStr">
@@ -4755,19 +4803,19 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Unit type</t>
+          <t>Total capacity</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr"/>
       <c r="F134" s="2" t="inlineStr"/>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
+          <t>Total capacity of void in cubic metres (or tonnes/litres)</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr">
@@ -4781,29 +4829,29 @@
       <c r="B135" s="2" t="n"/>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>Waste streams throughput</t>
+          <t>Waste management[]</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>Municipal</t>
+          <t>Unit type</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr"/>
       <c r="F135" s="2" t="inlineStr"/>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for municipal waste (annual throughput in tonnes/litres)</t>
+          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4812,19 +4860,19 @@
       <c r="B136" s="2" t="n"/>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Waste streams throughput</t>
+          <t>Waste management[]</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>Construction demolition</t>
+          <t>Annual throughput</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr"/>
       <c r="F136" s="2" t="inlineStr"/>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for construction and demolition waste (annual throughput in tonnes/litres)</t>
+          <t>Maximum annual operational throughput in tonnes/litres</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
@@ -4834,7 +4882,7 @@
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4843,29 +4891,29 @@
       <c r="B137" s="2" t="n"/>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>Waste streams throughput</t>
+          <t>Waste management[]</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>Commercial industrial</t>
+          <t>Unit type</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr"/>
       <c r="F137" s="2" t="inlineStr"/>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for commercial and industrial waste (annual throughput in tonnes/litres)</t>
+          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4879,14 +4927,14 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Hazardous</t>
+          <t>Municipal</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr"/>
       <c r="F138" s="2" t="inlineStr"/>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for hazardous waste (annual throughput in tonnes/litres)</t>
+          <t>Maximum throughput for municipal waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -4901,37 +4949,33 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="2" t="inlineStr">
-        <is>
-          <t>Description of the proposal</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>What development, works or change of use is proposed</t>
-        </is>
-      </c>
+      <c r="A139" s="2" t="n"/>
+      <c r="B139" s="2" t="n"/>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>Proposal description</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr"/>
+          <t>Waste streams throughput</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>Construction demolition</t>
+        </is>
+      </c>
       <c r="E139" s="2" t="inlineStr"/>
       <c r="F139" s="2" t="inlineStr"/>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>A description of what is being proposed, including the development, works, or change of use</t>
+          <t>Maximum throughput for construction and demolition waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4940,25 +4984,29 @@
       <c r="B140" s="2" t="n"/>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Reserved matters[]</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr"/>
+          <t>Waste streams throughput</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>Commercial industrial</t>
+        </is>
+      </c>
       <c r="E140" s="2" t="inlineStr"/>
       <c r="F140" s="2" t="inlineStr"/>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>Identifies which reserved matters are being submitted for approval as part of this application</t>
+          <t>Maximum throughput for commercial and industrial waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4967,34 +5015,46 @@
       <c r="B141" s="2" t="n"/>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>Proposal started</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr"/>
+          <t>Waste streams throughput</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>Hazardous</t>
+        </is>
+      </c>
       <c r="E141" s="2" t="inlineStr"/>
       <c r="F141" s="2" t="inlineStr"/>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been started</t>
+          <t>Maximum throughput for hazardous waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="n"/>
-      <c r="B142" s="2" t="n"/>
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>Description of the proposal</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>What development, works or change of use is proposed</t>
+        </is>
+      </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Proposal start date</t>
+          <t>Proposal description</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr"/>
@@ -5002,17 +5062,17 @@
       <c r="F142" s="2" t="inlineStr"/>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
+          <t>A description of what is being proposed, including the development, works, or change of use</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5021,7 +5081,7 @@
       <c r="B143" s="2" t="n"/>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>Proposal completed</t>
+          <t>Reserved matters[]</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr"/>
@@ -5029,12 +5089,12 @@
       <c r="F143" s="2" t="inlineStr"/>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been completed</t>
+          <t>Identifies which reserved matters are being submitted for approval as part of this application</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I143" s="2" t="inlineStr">
@@ -5048,7 +5108,7 @@
       <c r="B144" s="2" t="n"/>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Proposal completion date</t>
+          <t>Proposal started</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr"/>
@@ -5056,34 +5116,26 @@
       <c r="F144" s="2" t="inlineStr"/>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
+          <t>Has any work on the proposal already been started</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="2" t="inlineStr">
-        <is>
-          <t>Residential units</t>
-        </is>
-      </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>Details of the residential units that make up both the current and proposed development.</t>
-        </is>
-      </c>
+      <c r="A145" s="2" t="n"/>
+      <c r="B145" s="2" t="n"/>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>Residential unit change</t>
+          <t>Proposal start date</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr"/>
@@ -5091,17 +5143,17 @@
       <c r="F145" s="2" t="inlineStr"/>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>Proposal includes the gain, loss or change of use of residential units</t>
+          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5110,24 +5162,20 @@
       <c r="B146" s="2" t="n"/>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Residential unit summary[]</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
-        <is>
-          <t>Tenure type</t>
-        </is>
-      </c>
+          <t>Proposal completed</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr"/>
       <c r="E146" s="2" t="inlineStr"/>
       <c r="F146" s="2" t="inlineStr"/>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>Category of housing tenure</t>
+          <t>Has any work on the proposal already been completed</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr">
@@ -5141,54 +5189,50 @@
       <c r="B147" s="2" t="n"/>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>Residential unit summary[]</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
-        <is>
-          <t>Housing type</t>
-        </is>
-      </c>
+          <t>Proposal completion date</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr"/>
       <c r="E147" s="2" t="inlineStr"/>
       <c r="F147" s="2" t="inlineStr"/>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>Type of housing</t>
+          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="n"/>
-      <c r="B148" s="2" t="n"/>
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>Residential units</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>Details of the residential units that make up both the current and proposed development.</t>
+        </is>
+      </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Residential unit summary[]</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
-        <is>
-          <t>Existing unit breakdown[]</t>
-        </is>
-      </c>
-      <c r="E148" s="2" t="inlineStr">
-        <is>
-          <t>Units unknown</t>
-        </is>
-      </c>
+          <t>Residential unit change</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr"/>
+      <c r="E148" s="2" t="inlineStr"/>
       <c r="F148" s="2" t="inlineStr"/>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>Whether the number of units is unknown</t>
+          <t>Proposal includes the gain, loss or change of use of residential units</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -5212,27 +5256,19 @@
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>Existing unit breakdown[]</t>
-        </is>
-      </c>
-      <c r="E149" s="2" t="inlineStr">
-        <is>
-          <t>Units per bedroom number[]</t>
-        </is>
-      </c>
-      <c r="F149" s="2" t="inlineStr">
-        <is>
-          <t>No bedrooms unknown</t>
-        </is>
-      </c>
+          <t>Tenure type</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr"/>
+      <c r="F149" s="2" t="inlineStr"/>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>Set to true when counting units where bedroom number is unknown</t>
+          <t>Category of housing tenure</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I149" s="2" t="inlineStr">
@@ -5251,32 +5287,24 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>Existing unit breakdown[]</t>
-        </is>
-      </c>
-      <c r="E150" s="2" t="inlineStr">
-        <is>
-          <t>Units per bedroom number[]</t>
-        </is>
-      </c>
-      <c r="F150" s="2" t="inlineStr">
-        <is>
-          <t>Number of bedrooms</t>
-        </is>
-      </c>
+          <t>Housing type</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr"/>
+      <c r="F150" s="2" t="inlineStr"/>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>The number of bedrooms in unit</t>
+          <t>Type of housing</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5295,22 +5323,18 @@
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>Units per bedroom number[]</t>
-        </is>
-      </c>
-      <c r="F151" s="2" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
+          <t>Units unknown</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr"/>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>The number of units of that bedroom count</t>
+          <t>Whether the number of units is unknown</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I151" s="2" t="inlineStr">
@@ -5334,23 +5358,27 @@
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>Total units</t>
-        </is>
-      </c>
-      <c r="F152" s="2" t="inlineStr"/>
+          <t>Units per bedroom number[]</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>No bedrooms unknown</t>
+        </is>
+      </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>Total number of units</t>
+          <t>Set to true when counting units where bedroom number is unknown</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5364,28 +5392,32 @@
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>Proposed unit breakdown[]</t>
+          <t>Existing unit breakdown[]</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>Units unknown</t>
-        </is>
-      </c>
-      <c r="F153" s="2" t="inlineStr"/>
+          <t>Units per bedroom number[]</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>Number of bedrooms</t>
+        </is>
+      </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>Whether the number of units is unknown</t>
+          <t>The number of bedrooms in unit</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5399,7 +5431,7 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>Proposed unit breakdown[]</t>
+          <t>Existing unit breakdown[]</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
@@ -5409,17 +5441,17 @@
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>No bedrooms unknown</t>
+          <t>Units</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>Set to true when counting units where bedroom number is unknown</t>
+          <t>The number of units of that bedroom count</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr">
@@ -5438,22 +5470,18 @@
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>Proposed unit breakdown[]</t>
+          <t>Existing unit breakdown[]</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>Units per bedroom number[]</t>
-        </is>
-      </c>
-      <c r="F155" s="2" t="inlineStr">
-        <is>
-          <t>Number of bedrooms</t>
-        </is>
-      </c>
+          <t>Total units</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr"/>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>The number of bedrooms in unit</t>
+          <t>Total number of units</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -5482,22 +5510,18 @@
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>Units per bedroom number[]</t>
-        </is>
-      </c>
-      <c r="F156" s="2" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
+          <t>Units unknown</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr"/>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>The number of units of that bedroom count</t>
+          <t>Whether the number of units is unknown</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I156" s="2" t="inlineStr">
@@ -5521,23 +5545,27 @@
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>Total units</t>
-        </is>
-      </c>
-      <c r="F157" s="2" t="inlineStr"/>
+          <t>Units per bedroom number[]</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>No bedrooms unknown</t>
+        </is>
+      </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Total number of units</t>
+          <t>Set to true when counting units where bedroom number is unknown</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I157" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5546,15 +5574,27 @@
       <c r="B158" s="2" t="n"/>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>Total existing units</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr"/>
-      <c r="E158" s="2" t="inlineStr"/>
-      <c r="F158" s="2" t="inlineStr"/>
+          <t>Residential unit summary[]</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>Proposed unit breakdown[]</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>Units per bedroom number[]</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>Number of bedrooms</t>
+        </is>
+      </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>The total number of existing units</t>
+          <t>The number of bedrooms in unit</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
@@ -5564,7 +5604,7 @@
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5573,15 +5613,27 @@
       <c r="B159" s="2" t="n"/>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>Total proposed units</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr"/>
-      <c r="E159" s="2" t="inlineStr"/>
-      <c r="F159" s="2" t="inlineStr"/>
+          <t>Residential unit summary[]</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>Proposed unit breakdown[]</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>Units per bedroom number[]</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>The total number of proposed units</t>
+          <t>The number of units of that bedroom count</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -5600,15 +5652,23 @@
       <c r="B160" s="2" t="n"/>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Net change</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr"/>
-      <c r="E160" s="2" t="inlineStr"/>
+          <t>Residential unit summary[]</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>Proposed unit breakdown[]</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>Total units</t>
+        </is>
+      </c>
       <c r="F160" s="2" t="inlineStr"/>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>Calculated net change in units</t>
+          <t>Total number of units</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
@@ -5618,24 +5678,16 @@
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="2" t="inlineStr">
-        <is>
-          <t>Site area</t>
-        </is>
-      </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>How big the site is including relevant measurements</t>
-        </is>
-      </c>
+      <c r="A161" s="2" t="n"/>
+      <c r="B161" s="2" t="n"/>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>Site area in hectares</t>
+          <t>Total existing units</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr"/>
@@ -5643,12 +5695,12 @@
       <c r="F161" s="2" t="inlineStr"/>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>The size of the site in hectares</t>
+          <t>The total number of existing units</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I161" s="2" t="inlineStr">
@@ -5662,7 +5714,7 @@
       <c r="B162" s="2" t="n"/>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>Site area provided by</t>
+          <t>Total proposed units</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr"/>
@@ -5670,87 +5722,79 @@
       <c r="F162" s="2" t="inlineStr"/>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>Who provided the site area value</t>
+          <t>The total number of proposed units</t>
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="2" t="inlineStr">
-        <is>
-          <t>Site details</t>
-        </is>
-      </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>Where the proposed development will be built.</t>
-        </is>
-      </c>
+      <c r="A163" s="2" t="n"/>
+      <c r="B163" s="2" t="n"/>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="D163" s="2" t="inlineStr">
-        <is>
-          <t>Site boundary</t>
-        </is>
-      </c>
+          <t>Net change</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr"/>
       <c r="E163" s="2" t="inlineStr"/>
       <c r="F163" s="2" t="inlineStr"/>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>Geometry of the site of the development, typically in GeoJSON format</t>
+          <t>Calculated net change in units</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
-          <t>wkt</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I163" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="2" t="n"/>
-      <c r="B164" s="2" t="n"/>
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>Site area</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>How big the site is including relevant measurements</t>
+        </is>
+      </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="D164" s="2" t="inlineStr">
-        <is>
-          <t>Address Text</t>
-        </is>
-      </c>
+          <t>Site area in hectares</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr"/>
       <c r="E164" s="2" t="inlineStr"/>
       <c r="F164" s="2" t="inlineStr"/>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The size of the site in hectares</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5759,24 +5803,20 @@
       <c r="B165" s="2" t="n"/>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="D165" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Site area provided by</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr"/>
       <c r="E165" s="2" t="inlineStr"/>
       <c r="F165" s="2" t="inlineStr"/>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Who provided the site area value</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I165" s="2" t="inlineStr">
@@ -5786,8 +5826,16 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="n"/>
-      <c r="B166" s="2" t="n"/>
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>Site details</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>Where the proposed development will be built.</t>
+        </is>
+      </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
           <t>Site locations[]</t>
@@ -5795,24 +5843,24 @@
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>Easting</t>
+          <t>Site boundary</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr"/>
       <c r="F166" s="2" t="inlineStr"/>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
+          <t>A polygon or multipolygon boundary</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>multipolygon</t>
         </is>
       </c>
       <c r="I166" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5826,24 +5874,28 @@
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>Northing</t>
-        </is>
-      </c>
-      <c r="E167" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
       <c r="F167" s="2" t="inlineStr"/>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I167" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5857,19 +5909,23 @@
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>Latitude</t>
-        </is>
-      </c>
-      <c r="E168" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="F168" s="2" t="inlineStr"/>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I168" s="2" t="inlineStr">
@@ -5888,19 +5944,23 @@
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>Longitude</t>
-        </is>
-      </c>
-      <c r="E169" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>UPRNs[]</t>
+        </is>
+      </c>
       <c r="F169" s="2" t="inlineStr"/>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Unique Property Reference Numbers (UPRNs) for existing premises within a site boundary</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I169" s="2" t="inlineStr">
@@ -5919,14 +5979,18 @@
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="E170" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>USRNs[]</t>
+        </is>
+      </c>
       <c r="F170" s="2" t="inlineStr"/>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>A text description providing details about the subject.</t>
+          <t>Unique Street Reference Numbers (USRNs) associated with the site</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
@@ -5950,19 +6014,19 @@
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>UPRNs[]</t>
+          <t>Easting</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr"/>
       <c r="F171" s="2" t="inlineStr"/>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
+          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I171" s="2" t="inlineStr">
@@ -5972,37 +6036,33 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="2" t="inlineStr">
-        <is>
-          <t>Site Visit Details</t>
-        </is>
-      </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>Information to help the planning authority arrange a site visit</t>
-        </is>
-      </c>
+      <c r="A172" s="2" t="n"/>
+      <c r="B172" s="2" t="n"/>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>Site seen from public area</t>
-        </is>
-      </c>
-      <c r="D172" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>Northing</t>
+        </is>
+      </c>
       <c r="E172" s="2" t="inlineStr"/>
       <c r="F172" s="2" t="inlineStr"/>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
+          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -6011,25 +6071,29 @@
       <c r="B173" s="2" t="n"/>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>Site visit contact type</t>
-        </is>
-      </c>
-      <c r="D173" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Latitude</t>
+        </is>
+      </c>
       <c r="E173" s="2" t="inlineStr"/>
       <c r="F173" s="2" t="inlineStr"/>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>Indicates who the authority should contact to arrange a site visit</t>
+          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -6038,20 +6102,24 @@
       <c r="B174" s="2" t="n"/>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>Contact reference</t>
-        </is>
-      </c>
-      <c r="D174" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>Longitude</t>
+        </is>
+      </c>
       <c r="E174" s="2" t="inlineStr"/>
       <c r="F174" s="2" t="inlineStr"/>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="I174" s="2" t="inlineStr">
@@ -6061,28 +6129,32 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="2" t="n"/>
-      <c r="B175" s="2" t="n"/>
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>Site Visit Details</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>Information to help the planning authority arrange a site visit</t>
+        </is>
+      </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="D175" s="2" t="inlineStr">
-        <is>
-          <t>Full name</t>
-        </is>
-      </c>
+          <t>Site seen from public area</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr"/>
       <c r="E175" s="2" t="inlineStr"/>
       <c r="F175" s="2" t="inlineStr"/>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>The complete name of a person</t>
+          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I175" s="2" t="inlineStr">
@@ -6096,24 +6168,20 @@
       <c r="B176" s="2" t="n"/>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="D176" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Site visit contact type</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr"/>
       <c r="E176" s="2" t="inlineStr"/>
       <c r="F176" s="2" t="inlineStr"/>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>Indicates who the authority should contact to arrange a site visit</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I176" s="2" t="inlineStr">
@@ -6127,27 +6195,116 @@
       <c r="B177" s="2" t="n"/>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="D177" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Contact reference</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr"/>
       <c r="E177" s="2" t="inlineStr"/>
       <c r="F177" s="2" t="inlineStr"/>
       <c r="G177" s="2" t="inlineStr">
         <is>
+          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="n"/>
+      <c r="B178" s="2" t="n"/>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>Full name</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr"/>
+      <c r="F178" s="2" t="inlineStr"/>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>The complete name of a person</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="n"/>
+      <c r="B179" s="2" t="n"/>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>Phone number</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr"/>
+      <c r="F179" s="2" t="inlineStr"/>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>A phone number</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="n"/>
+      <c r="B180" s="2" t="n"/>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr"/>
+      <c r="F180" s="2" t="inlineStr"/>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
           <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
-      <c r="H177" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="I177" s="2" t="inlineStr">
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="inlineStr">
         <is>
           <t>MUST</t>
         </is>
@@ -6155,50 +6312,50 @@
     </row>
   </sheetData>
   <mergeCells count="44">
-    <mergeCell ref="A145:A160"/>
-    <mergeCell ref="A57:A59"/>
-    <mergeCell ref="A42:A55"/>
+    <mergeCell ref="A87:A93"/>
+    <mergeCell ref="B44:B57"/>
+    <mergeCell ref="A126:A130"/>
+    <mergeCell ref="A37:A43"/>
+    <mergeCell ref="B81:B86"/>
     <mergeCell ref="A2:A19"/>
-    <mergeCell ref="A24:A31"/>
-    <mergeCell ref="A36:A41"/>
-    <mergeCell ref="A172:A177"/>
-    <mergeCell ref="A79:A84"/>
-    <mergeCell ref="B161:B162"/>
-    <mergeCell ref="A163:A171"/>
-    <mergeCell ref="B92:B107"/>
-    <mergeCell ref="A85:A91"/>
-    <mergeCell ref="A108:A122"/>
-    <mergeCell ref="A92:A107"/>
-    <mergeCell ref="B123:B127"/>
-    <mergeCell ref="A69:A78"/>
-    <mergeCell ref="B128:B138"/>
-    <mergeCell ref="B63:B68"/>
-    <mergeCell ref="A32:A35"/>
-    <mergeCell ref="A123:A127"/>
-    <mergeCell ref="B56"/>
-    <mergeCell ref="A139:A144"/>
-    <mergeCell ref="A60:A62"/>
+    <mergeCell ref="B37:B43"/>
+    <mergeCell ref="A62:A64"/>
+    <mergeCell ref="A44:A57"/>
+    <mergeCell ref="A59:A61"/>
+    <mergeCell ref="A58"/>
+    <mergeCell ref="B87:B93"/>
+    <mergeCell ref="B166:B174"/>
+    <mergeCell ref="B71:B80"/>
+    <mergeCell ref="B126:B130"/>
+    <mergeCell ref="A164:A165"/>
+    <mergeCell ref="B24:B32"/>
+    <mergeCell ref="A33:A36"/>
+    <mergeCell ref="B110:B125"/>
+    <mergeCell ref="B59:B61"/>
+    <mergeCell ref="A65:A70"/>
+    <mergeCell ref="B62:B64"/>
+    <mergeCell ref="A131:A141"/>
+    <mergeCell ref="B175:B180"/>
+    <mergeCell ref="B58"/>
+    <mergeCell ref="B94:B109"/>
+    <mergeCell ref="A110:A125"/>
+    <mergeCell ref="A148:A163"/>
     <mergeCell ref="A20:A23"/>
-    <mergeCell ref="B85:B91"/>
-    <mergeCell ref="B172:B177"/>
-    <mergeCell ref="B108:B122"/>
-    <mergeCell ref="B69:B78"/>
-    <mergeCell ref="B163:B171"/>
-    <mergeCell ref="B145:B160"/>
-    <mergeCell ref="B36:B41"/>
-    <mergeCell ref="A56"/>
-    <mergeCell ref="B57:B59"/>
-    <mergeCell ref="A161:A162"/>
-    <mergeCell ref="B139:B144"/>
+    <mergeCell ref="B164:B165"/>
+    <mergeCell ref="A175:A180"/>
+    <mergeCell ref="B33:B36"/>
+    <mergeCell ref="A94:A109"/>
+    <mergeCell ref="A71:A80"/>
+    <mergeCell ref="B142:B147"/>
+    <mergeCell ref="B65:B70"/>
+    <mergeCell ref="A166:A174"/>
+    <mergeCell ref="B131:B141"/>
+    <mergeCell ref="A24:A32"/>
     <mergeCell ref="B20:B23"/>
-    <mergeCell ref="B42:B55"/>
-    <mergeCell ref="B60:B62"/>
-    <mergeCell ref="A63:A68"/>
+    <mergeCell ref="B148:B163"/>
+    <mergeCell ref="A81:A86"/>
     <mergeCell ref="B2:B19"/>
-    <mergeCell ref="B24:B31"/>
-    <mergeCell ref="B32:B35"/>
-    <mergeCell ref="A128:A138"/>
-    <mergeCell ref="B79:B84"/>
+    <mergeCell ref="A142:A147"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
